--- a/booklist/第二屆_核心書單.xlsx
+++ b/booklist/第二屆_核心書單.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\a0963\OneDrive\Pictures\桌面\habbitualreader\booklist\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{039F0A73-4D81-45EA-9CC2-0FC99DFFC48E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{18A90436-9128-4BA6-8AF9-4A80DB6D83F0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-28920" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{D6089884-307B-4EF6-ABDF-EA2F9AAD2605}"/>
   </bookViews>
@@ -39,10 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="579" uniqueCount="169">
-  <si>
-    <t>2年級</t>
-  </si>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="579" uniqueCount="165">
   <si>
     <t>讓世界更好：創意回收救地球的真實故事</t>
     <phoneticPr fontId="2" type="noConversion"/>
@@ -80,10 +77,6 @@
     <t>隱形男孩</t>
   </si>
   <si>
-    <t>2年級</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
     <t>一顆海龜蛋的神奇旅程</t>
   </si>
   <si>
@@ -148,10 +141,6 @@
   </si>
   <si>
     <t>阿婆的燈籠樹（二版）</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>4年級</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
@@ -162,9 +151,6 @@
 人文社會</t>
   </si>
   <si>
-    <t>4年級</t>
-  </si>
-  <si>
     <t>晨讀10分鐘：成語故事集</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
@@ -242,9 +228,6 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>6年級</t>
-  </si>
-  <si>
     <t>SDGs系列講堂 牽動全球的水資源與環境問題：建立永續循環的水文化，解決刻不容緩的缺水、淹水與汙染問題</t>
   </si>
   <si>
@@ -272,10 +255,6 @@
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
-    <t>國中</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
     <t>一把蓮：黑水溝傳奇</t>
   </si>
   <si>
@@ -356,10 +335,6 @@
   </si>
   <si>
     <t>勇闖宇宙首部曲：卡斯摩的祕密</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>高中</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
@@ -426,10 +401,6 @@
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
-    <t>6年級</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>人文社會
 科學技術</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -440,10 +411,6 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>6年級</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
     <t>年級</t>
   </si>
   <si>
@@ -643,6 +610,26 @@
   <si>
     <t>核心書籍</t>
     <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>國小二年級</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>國小四年級</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>國小六年級</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>國中級</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>高中級</t>
+    <phoneticPr fontId="2" type="noConversion"/>
   </si>
 </sst>
 </file>
@@ -2237,7 +2224,7 @@
   <dimension ref="A1:V113"/>
   <sheetFormatPr defaultRowHeight="17" x14ac:dyDescent="0.4"/>
   <cols>
-    <col min="1" max="1" width="6.81640625" style="5" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="15.453125" style="5" customWidth="1"/>
     <col min="2" max="2" width="51.6328125" style="5" customWidth="1"/>
     <col min="3" max="3" width="17.08984375" style="5" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="11.7265625" style="5" customWidth="1"/>
@@ -2246,24 +2233,24 @@
     <col min="7" max="16384" width="8.7265625" style="5"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:22" s="5" customFormat="1" ht="21.5" x14ac:dyDescent="0.4">
+    <row r="1" spans="1:22" ht="21.5" x14ac:dyDescent="0.4">
       <c r="A1" s="1" t="s">
-        <v>113</v>
+        <v>104</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>114</v>
+        <v>105</v>
       </c>
       <c r="C1" s="2" t="s">
-        <v>115</v>
+        <v>106</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>165</v>
+        <v>156</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>166</v>
+        <v>157</v>
       </c>
       <c r="F1" s="3" t="s">
-        <v>167</v>
+        <v>158</v>
       </c>
       <c r="G1" s="4"/>
       <c r="H1" s="4"/>
@@ -2284,22 +2271,22 @@
     </row>
     <row r="2" spans="1:22" s="4" customFormat="1" ht="34" x14ac:dyDescent="0.4">
       <c r="A2" s="7" t="s">
+        <v>160</v>
+      </c>
+      <c r="B2" s="7" t="s">
         <v>0</v>
-      </c>
-      <c r="B2" s="7" t="s">
-        <v>1</v>
       </c>
       <c r="C2" s="8">
         <v>9789860641790</v>
       </c>
       <c r="D2" s="9" t="s">
+        <v>1</v>
+      </c>
+      <c r="E2" s="7" t="s">
         <v>2</v>
       </c>
-      <c r="E2" s="7" t="s">
-        <v>3</v>
-      </c>
       <c r="F2" s="4" t="s">
-        <v>168</v>
+        <v>159</v>
       </c>
       <c r="G2" s="7"/>
       <c r="H2" s="7"/>
@@ -2320,22 +2307,22 @@
     </row>
     <row r="3" spans="1:22" s="4" customFormat="1" ht="34" x14ac:dyDescent="0.4">
       <c r="A3" s="7" t="s">
-        <v>0</v>
+        <v>160</v>
       </c>
       <c r="B3" s="7" t="s">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="C3" s="10">
         <v>9789860610222</v>
       </c>
       <c r="D3" s="9" t="s">
+        <v>4</v>
+      </c>
+      <c r="E3" s="11" t="s">
         <v>5</v>
       </c>
-      <c r="E3" s="11" t="s">
-        <v>6</v>
-      </c>
       <c r="F3" s="4" t="s">
-        <v>168</v>
+        <v>159</v>
       </c>
       <c r="G3" s="7"/>
       <c r="H3" s="7"/>
@@ -2356,22 +2343,22 @@
     </row>
     <row r="4" spans="1:22" s="4" customFormat="1" ht="34" x14ac:dyDescent="0.4">
       <c r="A4" s="7" t="s">
-        <v>0</v>
+        <v>160</v>
       </c>
       <c r="B4" s="11" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="C4" s="10">
         <v>9789863384151</v>
       </c>
       <c r="D4" s="11" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="E4" s="11" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="F4" s="4" t="s">
-        <v>168</v>
+        <v>159</v>
       </c>
       <c r="G4" s="7"/>
       <c r="H4" s="7"/>
@@ -2390,24 +2377,24 @@
       <c r="U4" s="7"/>
       <c r="V4" s="7"/>
     </row>
-    <row r="5" spans="1:22" s="5" customFormat="1" ht="34" x14ac:dyDescent="0.4">
-      <c r="A5" s="4" t="s">
-        <v>0</v>
+    <row r="5" spans="1:22" ht="34" x14ac:dyDescent="0.4">
+      <c r="A5" s="7" t="s">
+        <v>160</v>
       </c>
       <c r="B5" s="4" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="C5" s="10">
         <v>9789578640931</v>
       </c>
       <c r="D5" s="11" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="E5" s="4" t="s">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="F5" s="4" t="s">
-        <v>168</v>
+        <v>159</v>
       </c>
       <c r="G5" s="6"/>
       <c r="H5" s="6"/>
@@ -2426,24 +2413,24 @@
       <c r="U5" s="6"/>
       <c r="V5" s="6"/>
     </row>
-    <row r="6" spans="1:22" s="5" customFormat="1" ht="34" x14ac:dyDescent="0.4">
+    <row r="6" spans="1:22" ht="34" x14ac:dyDescent="0.4">
       <c r="A6" s="7" t="s">
-        <v>0</v>
+        <v>160</v>
       </c>
       <c r="B6" s="4" t="s">
-        <v>139</v>
+        <v>130</v>
       </c>
       <c r="C6" s="12">
         <v>9789865251635</v>
       </c>
       <c r="D6" s="11" t="s">
+        <v>1</v>
+      </c>
+      <c r="E6" s="4" t="s">
         <v>2</v>
       </c>
-      <c r="E6" s="4" t="s">
-        <v>3</v>
-      </c>
       <c r="F6" s="4" t="s">
-        <v>168</v>
+        <v>159</v>
       </c>
       <c r="G6" s="4"/>
       <c r="H6" s="4"/>
@@ -2462,24 +2449,24 @@
       <c r="U6" s="4"/>
       <c r="V6" s="4"/>
     </row>
-    <row r="7" spans="1:22" s="5" customFormat="1" ht="34" x14ac:dyDescent="0.4">
-      <c r="A7" s="4" t="s">
-        <v>10</v>
+    <row r="7" spans="1:22" ht="34" x14ac:dyDescent="0.4">
+      <c r="A7" s="7" t="s">
+        <v>160</v>
       </c>
       <c r="B7" s="4" t="s">
-        <v>140</v>
+        <v>131</v>
       </c>
       <c r="C7" s="13">
         <v>9789860645170</v>
       </c>
       <c r="D7" s="11" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="E7" s="4" t="s">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="F7" s="4" t="s">
-        <v>168</v>
+        <v>159</v>
       </c>
       <c r="G7" s="6"/>
       <c r="H7" s="6"/>
@@ -2498,24 +2485,24 @@
       <c r="U7" s="6"/>
       <c r="V7" s="6"/>
     </row>
-    <row r="8" spans="1:22" s="5" customFormat="1" ht="34" x14ac:dyDescent="0.4">
-      <c r="A8" s="4" t="s">
-        <v>10</v>
+    <row r="8" spans="1:22" ht="34" x14ac:dyDescent="0.4">
+      <c r="A8" s="7" t="s">
+        <v>160</v>
       </c>
       <c r="B8" s="4" t="s">
-        <v>141</v>
+        <v>132</v>
       </c>
       <c r="C8" s="10">
         <v>9789576428289</v>
       </c>
       <c r="D8" s="11" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="E8" s="4" t="s">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="F8" s="4" t="s">
-        <v>168</v>
+        <v>159</v>
       </c>
       <c r="G8" s="6"/>
       <c r="H8" s="6"/>
@@ -2534,24 +2521,24 @@
       <c r="U8" s="6"/>
       <c r="V8" s="6"/>
     </row>
-    <row r="9" spans="1:22" s="5" customFormat="1" x14ac:dyDescent="0.4">
-      <c r="A9" s="4" t="s">
-        <v>0</v>
+    <row r="9" spans="1:22" x14ac:dyDescent="0.4">
+      <c r="A9" s="7" t="s">
+        <v>160</v>
       </c>
       <c r="B9" s="11" t="s">
+        <v>9</v>
+      </c>
+      <c r="C9" s="10" t="s">
+        <v>10</v>
+      </c>
+      <c r="D9" s="4" t="s">
         <v>11</v>
       </c>
-      <c r="C9" s="10" t="s">
-        <v>12</v>
-      </c>
-      <c r="D9" s="4" t="s">
-        <v>13</v>
-      </c>
       <c r="E9" s="4" t="s">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="F9" s="4" t="s">
-        <v>168</v>
+        <v>159</v>
       </c>
       <c r="G9" s="4"/>
       <c r="H9" s="4"/>
@@ -2570,24 +2557,24 @@
       <c r="U9" s="4"/>
       <c r="V9" s="4"/>
     </row>
-    <row r="10" spans="1:22" s="5" customFormat="1" x14ac:dyDescent="0.4">
-      <c r="A10" s="4" t="s">
-        <v>0</v>
+    <row r="10" spans="1:22" x14ac:dyDescent="0.4">
+      <c r="A10" s="7" t="s">
+        <v>160</v>
       </c>
       <c r="B10" s="14" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="C10" s="13">
         <v>9789576584756</v>
       </c>
       <c r="D10" s="4" t="s">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="E10" s="4" t="s">
-        <v>108</v>
+        <v>101</v>
       </c>
       <c r="F10" s="4" t="s">
-        <v>168</v>
+        <v>159</v>
       </c>
       <c r="G10" s="6"/>
       <c r="H10" s="6"/>
@@ -2606,24 +2593,24 @@
       <c r="U10" s="6"/>
       <c r="V10" s="6"/>
     </row>
-    <row r="11" spans="1:22" s="5" customFormat="1" x14ac:dyDescent="0.4">
-      <c r="A11" s="4" t="s">
-        <v>0</v>
+    <row r="11" spans="1:22" x14ac:dyDescent="0.4">
+      <c r="A11" s="7" t="s">
+        <v>160</v>
       </c>
       <c r="B11" s="4" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="C11" s="10">
         <v>9789579125796</v>
       </c>
       <c r="D11" s="4" t="s">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="E11" s="4" t="s">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="F11" s="4" t="s">
-        <v>168</v>
+        <v>159</v>
       </c>
       <c r="G11" s="4"/>
       <c r="H11" s="4"/>
@@ -2642,24 +2629,24 @@
       <c r="U11" s="4"/>
       <c r="V11" s="4"/>
     </row>
-    <row r="12" spans="1:22" s="5" customFormat="1" x14ac:dyDescent="0.4">
-      <c r="A12" s="4" t="s">
-        <v>0</v>
+    <row r="12" spans="1:22" x14ac:dyDescent="0.4">
+      <c r="A12" s="7" t="s">
+        <v>160</v>
       </c>
       <c r="B12" s="11" t="s">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="C12" s="10" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="D12" s="4" t="s">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="E12" s="4" t="s">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="F12" s="4" t="s">
-        <v>168</v>
+        <v>159</v>
       </c>
       <c r="G12" s="4"/>
       <c r="H12" s="4"/>
@@ -2678,24 +2665,24 @@
       <c r="U12" s="4"/>
       <c r="V12" s="4"/>
     </row>
-    <row r="13" spans="1:22" s="5" customFormat="1" x14ac:dyDescent="0.4">
-      <c r="A13" s="4" t="s">
-        <v>10</v>
+    <row r="13" spans="1:22" x14ac:dyDescent="0.4">
+      <c r="A13" s="7" t="s">
+        <v>160</v>
       </c>
       <c r="B13" s="4" t="s">
-        <v>142</v>
+        <v>133</v>
       </c>
       <c r="C13" s="10">
         <v>9789863597490</v>
       </c>
       <c r="D13" s="4" t="s">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="E13" s="4" t="s">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="F13" s="4" t="s">
-        <v>168</v>
+        <v>159</v>
       </c>
       <c r="G13" s="4"/>
       <c r="H13" s="4"/>
@@ -2714,24 +2701,24 @@
       <c r="U13" s="4"/>
       <c r="V13" s="4"/>
     </row>
-    <row r="14" spans="1:22" s="5" customFormat="1" x14ac:dyDescent="0.4">
-      <c r="A14" s="4" t="s">
-        <v>0</v>
+    <row r="14" spans="1:22" x14ac:dyDescent="0.4">
+      <c r="A14" s="7" t="s">
+        <v>160</v>
       </c>
       <c r="B14" s="4" t="s">
-        <v>143</v>
+        <v>134</v>
       </c>
       <c r="C14" s="10">
         <v>9789573294269</v>
       </c>
       <c r="D14" s="4" t="s">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="E14" s="4" t="s">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="F14" s="4" t="s">
-        <v>168</v>
+        <v>159</v>
       </c>
       <c r="G14" s="4"/>
       <c r="H14" s="4"/>
@@ -2750,24 +2737,24 @@
       <c r="U14" s="4"/>
       <c r="V14" s="4"/>
     </row>
-    <row r="15" spans="1:22" s="5" customFormat="1" x14ac:dyDescent="0.4">
-      <c r="A15" s="6" t="s">
-        <v>0</v>
+    <row r="15" spans="1:22" x14ac:dyDescent="0.4">
+      <c r="A15" s="7" t="s">
+        <v>160</v>
       </c>
       <c r="B15" s="15" t="s">
-        <v>144</v>
+        <v>135</v>
       </c>
       <c r="C15" s="16">
         <v>9786267043691</v>
       </c>
       <c r="D15" s="17" t="s">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="E15" s="4" t="s">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="F15" s="4" t="s">
-        <v>168</v>
+        <v>159</v>
       </c>
       <c r="G15" s="4"/>
       <c r="H15" s="4"/>
@@ -2786,24 +2773,24 @@
       <c r="U15" s="4"/>
       <c r="V15" s="4"/>
     </row>
-    <row r="16" spans="1:22" s="5" customFormat="1" x14ac:dyDescent="0.4">
-      <c r="A16" s="4" t="s">
-        <v>0</v>
+    <row r="16" spans="1:22" x14ac:dyDescent="0.4">
+      <c r="A16" s="7" t="s">
+        <v>160</v>
       </c>
       <c r="B16" s="14" t="s">
-        <v>145</v>
+        <v>136</v>
       </c>
       <c r="C16" s="13">
         <v>9789570838466</v>
       </c>
       <c r="D16" s="4" t="s">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="E16" s="4" t="s">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="F16" s="4" t="s">
-        <v>168</v>
+        <v>159</v>
       </c>
       <c r="G16" s="6"/>
       <c r="H16" s="6"/>
@@ -2824,22 +2811,22 @@
     </row>
     <row r="17" spans="1:22" s="4" customFormat="1" x14ac:dyDescent="0.4">
       <c r="A17" s="7" t="s">
-        <v>0</v>
+        <v>160</v>
       </c>
       <c r="B17" s="10" t="s">
-        <v>146</v>
+        <v>137</v>
       </c>
       <c r="C17" s="10">
         <v>9789866407093</v>
       </c>
       <c r="D17" s="4" t="s">
-        <v>74</v>
+        <v>68</v>
       </c>
       <c r="E17" s="4" t="s">
-        <v>108</v>
+        <v>101</v>
       </c>
       <c r="F17" s="4" t="s">
-        <v>168</v>
+        <v>159</v>
       </c>
       <c r="G17" s="7"/>
       <c r="H17" s="7"/>
@@ -2858,24 +2845,24 @@
       <c r="U17" s="7"/>
       <c r="V17" s="7"/>
     </row>
-    <row r="18" spans="1:22" s="5" customFormat="1" x14ac:dyDescent="0.4">
-      <c r="A18" s="4" t="s">
-        <v>0</v>
+    <row r="18" spans="1:22" x14ac:dyDescent="0.4">
+      <c r="A18" s="7" t="s">
+        <v>160</v>
       </c>
       <c r="B18" s="4" t="s">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="C18" s="10" t="s">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="D18" s="4" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="E18" s="4" t="s">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="F18" s="4" t="s">
-        <v>168</v>
+        <v>159</v>
       </c>
       <c r="G18" s="4"/>
       <c r="H18" s="4"/>
@@ -2894,24 +2881,24 @@
       <c r="U18" s="4"/>
       <c r="V18" s="4"/>
     </row>
-    <row r="19" spans="1:22" s="5" customFormat="1" x14ac:dyDescent="0.4">
-      <c r="A19" s="4" t="s">
-        <v>0</v>
+    <row r="19" spans="1:22" x14ac:dyDescent="0.4">
+      <c r="A19" s="7" t="s">
+        <v>160</v>
       </c>
       <c r="B19" s="4" t="s">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="C19" s="12">
         <v>9789864001750</v>
       </c>
       <c r="D19" s="4" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="E19" s="4" t="s">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="F19" s="4" t="s">
-        <v>168</v>
+        <v>159</v>
       </c>
       <c r="G19" s="4"/>
       <c r="H19" s="4"/>
@@ -2930,24 +2917,24 @@
       <c r="U19" s="4"/>
       <c r="V19" s="4"/>
     </row>
-    <row r="20" spans="1:22" s="5" customFormat="1" x14ac:dyDescent="0.4">
-      <c r="A20" s="4" t="s">
-        <v>0</v>
+    <row r="20" spans="1:22" x14ac:dyDescent="0.4">
+      <c r="A20" s="7" t="s">
+        <v>160</v>
       </c>
       <c r="B20" s="4" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="C20" s="18" t="s">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="D20" s="4" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="E20" s="4" t="s">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="F20" s="4" t="s">
-        <v>168</v>
+        <v>159</v>
       </c>
       <c r="G20" s="4"/>
       <c r="H20" s="4"/>
@@ -2966,24 +2953,24 @@
       <c r="U20" s="4"/>
       <c r="V20" s="4"/>
     </row>
-    <row r="21" spans="1:22" s="5" customFormat="1" x14ac:dyDescent="0.4">
-      <c r="A21" s="4" t="s">
-        <v>10</v>
+    <row r="21" spans="1:22" x14ac:dyDescent="0.4">
+      <c r="A21" s="7" t="s">
+        <v>160</v>
       </c>
       <c r="B21" s="4" t="s">
-        <v>147</v>
+        <v>138</v>
       </c>
       <c r="C21" s="10" t="s">
-        <v>148</v>
+        <v>139</v>
       </c>
       <c r="D21" s="4" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="E21" s="4" t="s">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="F21" s="4" t="s">
-        <v>168</v>
+        <v>159</v>
       </c>
       <c r="G21" s="4"/>
       <c r="H21" s="4"/>
@@ -3002,24 +2989,24 @@
       <c r="U21" s="4"/>
       <c r="V21" s="4"/>
     </row>
-    <row r="22" spans="1:22" s="5" customFormat="1" x14ac:dyDescent="0.4">
-      <c r="A22" s="4" t="s">
-        <v>0</v>
+    <row r="22" spans="1:22" x14ac:dyDescent="0.4">
+      <c r="A22" s="7" t="s">
+        <v>160</v>
       </c>
       <c r="B22" s="11" t="s">
-        <v>149</v>
+        <v>140</v>
       </c>
       <c r="C22" s="18" t="s">
-        <v>150</v>
+        <v>141</v>
       </c>
       <c r="D22" s="4" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="E22" s="4" t="s">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="F22" s="4" t="s">
-        <v>168</v>
+        <v>159</v>
       </c>
       <c r="G22" s="4"/>
       <c r="H22" s="4"/>
@@ -3038,24 +3025,24 @@
       <c r="U22" s="4"/>
       <c r="V22" s="4"/>
     </row>
-    <row r="23" spans="1:22" s="5" customFormat="1" x14ac:dyDescent="0.4">
-      <c r="A23" s="4" t="s">
-        <v>0</v>
+    <row r="23" spans="1:22" x14ac:dyDescent="0.4">
+      <c r="A23" s="7" t="s">
+        <v>160</v>
       </c>
       <c r="B23" s="11" t="s">
-        <v>151</v>
+        <v>142</v>
       </c>
       <c r="C23" s="18" t="s">
-        <v>152</v>
+        <v>143</v>
       </c>
       <c r="D23" s="4" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="E23" s="4" t="s">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="F23" s="4" t="s">
-        <v>168</v>
+        <v>159</v>
       </c>
       <c r="G23" s="4"/>
       <c r="H23" s="4"/>
@@ -3074,24 +3061,24 @@
       <c r="U23" s="4"/>
       <c r="V23" s="4"/>
     </row>
-    <row r="24" spans="1:22" s="5" customFormat="1" x14ac:dyDescent="0.4">
-      <c r="A24" s="4" t="s">
-        <v>0</v>
+    <row r="24" spans="1:22" x14ac:dyDescent="0.4">
+      <c r="A24" s="7" t="s">
+        <v>160</v>
       </c>
       <c r="B24" s="4" t="s">
-        <v>153</v>
+        <v>144</v>
       </c>
       <c r="C24" s="18" t="s">
-        <v>154</v>
+        <v>145</v>
       </c>
       <c r="D24" s="4" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="E24" s="4" t="s">
-        <v>155</v>
+        <v>146</v>
       </c>
       <c r="F24" s="4" t="s">
-        <v>168</v>
+        <v>159</v>
       </c>
       <c r="G24" s="4"/>
       <c r="H24" s="4"/>
@@ -3110,24 +3097,24 @@
       <c r="U24" s="4"/>
       <c r="V24" s="4"/>
     </row>
-    <row r="25" spans="1:22" s="5" customFormat="1" x14ac:dyDescent="0.4">
-      <c r="A25" s="4" t="s">
-        <v>0</v>
+    <row r="25" spans="1:22" x14ac:dyDescent="0.4">
+      <c r="A25" s="7" t="s">
+        <v>160</v>
       </c>
       <c r="B25" s="4" t="s">
-        <v>156</v>
+        <v>147</v>
       </c>
       <c r="C25" s="18" t="s">
-        <v>157</v>
+        <v>148</v>
       </c>
       <c r="D25" s="4" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="E25" s="4" t="s">
-        <v>155</v>
+        <v>146</v>
       </c>
       <c r="F25" s="4" t="s">
-        <v>168</v>
+        <v>159</v>
       </c>
       <c r="G25" s="4"/>
       <c r="H25" s="4"/>
@@ -3146,24 +3133,24 @@
       <c r="U25" s="4"/>
       <c r="V25" s="4"/>
     </row>
-    <row r="26" spans="1:22" s="5" customFormat="1" x14ac:dyDescent="0.4">
-      <c r="A26" s="4" t="s">
-        <v>0</v>
+    <row r="26" spans="1:22" x14ac:dyDescent="0.4">
+      <c r="A26" s="7" t="s">
+        <v>160</v>
       </c>
       <c r="B26" s="4" t="s">
+        <v>24</v>
+      </c>
+      <c r="C26" s="10" t="s">
+        <v>25</v>
+      </c>
+      <c r="D26" s="4" t="s">
         <v>26</v>
       </c>
-      <c r="C26" s="10" t="s">
-        <v>27</v>
-      </c>
-      <c r="D26" s="4" t="s">
-        <v>28</v>
-      </c>
       <c r="E26" s="4" t="s">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="F26" s="4" t="s">
-        <v>168</v>
+        <v>159</v>
       </c>
       <c r="G26" s="4"/>
       <c r="H26" s="4"/>
@@ -3182,24 +3169,24 @@
       <c r="U26" s="4"/>
       <c r="V26" s="4"/>
     </row>
-    <row r="27" spans="1:22" s="5" customFormat="1" x14ac:dyDescent="0.4">
-      <c r="A27" s="6" t="s">
-        <v>0</v>
+    <row r="27" spans="1:22" x14ac:dyDescent="0.4">
+      <c r="A27" s="7" t="s">
+        <v>160</v>
       </c>
       <c r="B27" s="4" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="C27" s="12">
         <v>9789864403752</v>
       </c>
       <c r="D27" s="19" t="s">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="E27" s="4" t="s">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="F27" s="4" t="s">
-        <v>168</v>
+        <v>159</v>
       </c>
       <c r="G27" s="4"/>
       <c r="H27" s="4"/>
@@ -3218,24 +3205,24 @@
       <c r="U27" s="4"/>
       <c r="V27" s="4"/>
     </row>
-    <row r="28" spans="1:22" s="5" customFormat="1" x14ac:dyDescent="0.4">
-      <c r="A28" s="4" t="s">
-        <v>0</v>
+    <row r="28" spans="1:22" x14ac:dyDescent="0.4">
+      <c r="A28" s="7" t="s">
+        <v>160</v>
       </c>
       <c r="B28" s="4" t="s">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="C28" s="12">
         <v>9786267043011</v>
       </c>
       <c r="D28" s="4" t="s">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="E28" s="4" t="s">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="F28" s="4" t="s">
-        <v>168</v>
+        <v>159</v>
       </c>
       <c r="G28" s="6"/>
       <c r="H28" s="6"/>
@@ -3254,24 +3241,24 @@
       <c r="U28" s="6"/>
       <c r="V28" s="6"/>
     </row>
-    <row r="29" spans="1:22" s="5" customFormat="1" x14ac:dyDescent="0.4">
-      <c r="A29" s="4" t="s">
-        <v>0</v>
+    <row r="29" spans="1:22" x14ac:dyDescent="0.4">
+      <c r="A29" s="7" t="s">
+        <v>160</v>
       </c>
       <c r="B29" s="4" t="s">
-        <v>158</v>
+        <v>149</v>
       </c>
       <c r="C29" s="12">
         <v>9789866049538</v>
       </c>
       <c r="D29" s="4" t="s">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="E29" s="4" t="s">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="F29" s="4" t="s">
-        <v>168</v>
+        <v>159</v>
       </c>
       <c r="G29" s="6"/>
       <c r="H29" s="6"/>
@@ -3290,24 +3277,24 @@
       <c r="U29" s="4"/>
       <c r="V29" s="4"/>
     </row>
-    <row r="30" spans="1:22" s="5" customFormat="1" x14ac:dyDescent="0.4">
-      <c r="A30" s="4" t="s">
-        <v>0</v>
+    <row r="30" spans="1:22" x14ac:dyDescent="0.4">
+      <c r="A30" s="7" t="s">
+        <v>160</v>
       </c>
       <c r="B30" s="4" t="s">
-        <v>159</v>
+        <v>150</v>
       </c>
       <c r="C30" s="12">
         <v>9789865811327</v>
       </c>
       <c r="D30" s="4" t="s">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="E30" s="4" t="s">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="F30" s="4" t="s">
-        <v>168</v>
+        <v>159</v>
       </c>
       <c r="G30" s="4"/>
       <c r="H30" s="4"/>
@@ -3326,24 +3313,24 @@
       <c r="U30" s="4"/>
       <c r="V30" s="4"/>
     </row>
-    <row r="31" spans="1:22" s="5" customFormat="1" x14ac:dyDescent="0.4">
-      <c r="A31" s="4" t="s">
-        <v>0</v>
+    <row r="31" spans="1:22" x14ac:dyDescent="0.4">
+      <c r="A31" s="7" t="s">
+        <v>160</v>
       </c>
       <c r="B31" s="11" t="s">
-        <v>160</v>
+        <v>151</v>
       </c>
       <c r="C31" s="10">
         <v>9789864400591</v>
       </c>
       <c r="D31" s="4" t="s">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="E31" s="4" t="s">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="F31" s="4" t="s">
-        <v>168</v>
+        <v>159</v>
       </c>
       <c r="G31" s="4"/>
       <c r="H31" s="4"/>
@@ -3362,24 +3349,24 @@
       <c r="U31" s="4"/>
       <c r="V31" s="4"/>
     </row>
-    <row r="32" spans="1:22" s="5" customFormat="1" x14ac:dyDescent="0.4">
-      <c r="A32" s="6" t="s">
-        <v>0</v>
+    <row r="32" spans="1:22" x14ac:dyDescent="0.4">
+      <c r="A32" s="7" t="s">
+        <v>160</v>
       </c>
       <c r="B32" s="4" t="s">
-        <v>161</v>
+        <v>152</v>
       </c>
       <c r="C32" s="18" t="s">
-        <v>162</v>
+        <v>153</v>
       </c>
       <c r="D32" s="4" t="s">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="E32" s="4" t="s">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="F32" s="4" t="s">
-        <v>168</v>
+        <v>159</v>
       </c>
       <c r="G32" s="6"/>
       <c r="H32" s="6"/>
@@ -3398,24 +3385,24 @@
       <c r="U32" s="6"/>
       <c r="V32" s="6"/>
     </row>
-    <row r="33" spans="1:22" s="5" customFormat="1" x14ac:dyDescent="0.4">
-      <c r="A33" s="6" t="s">
-        <v>0</v>
+    <row r="33" spans="1:22" x14ac:dyDescent="0.4">
+      <c r="A33" s="7" t="s">
+        <v>160</v>
       </c>
       <c r="B33" s="4" t="s">
-        <v>163</v>
+        <v>154</v>
       </c>
       <c r="C33" s="18" t="s">
-        <v>164</v>
+        <v>155</v>
       </c>
       <c r="D33" s="4" t="s">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="E33" s="4" t="s">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="F33" s="4" t="s">
-        <v>168</v>
+        <v>159</v>
       </c>
       <c r="G33" s="6"/>
       <c r="H33" s="6"/>
@@ -3434,24 +3421,24 @@
       <c r="U33" s="6"/>
       <c r="V33" s="6"/>
     </row>
-    <row r="34" spans="1:22" s="5" customFormat="1" ht="34" x14ac:dyDescent="0.4">
+    <row r="34" spans="1:22" ht="34" x14ac:dyDescent="0.4">
       <c r="A34" s="7" t="s">
-        <v>31</v>
+        <v>161</v>
       </c>
       <c r="B34" s="7" t="s">
-        <v>32</v>
+        <v>29</v>
       </c>
       <c r="C34" s="8">
         <v>9789577515896</v>
       </c>
       <c r="D34" s="20" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="E34" s="7" t="s">
-        <v>108</v>
+        <v>101</v>
       </c>
       <c r="F34" s="4" t="s">
-        <v>168</v>
+        <v>159</v>
       </c>
       <c r="G34" s="6"/>
       <c r="H34" s="6"/>
@@ -3468,24 +3455,24 @@
       <c r="S34" s="4"/>
       <c r="T34" s="4"/>
     </row>
-    <row r="35" spans="1:22" s="5" customFormat="1" ht="34" x14ac:dyDescent="0.4">
-      <c r="A35" s="6" t="s">
-        <v>34</v>
+    <row r="35" spans="1:22" ht="34" x14ac:dyDescent="0.4">
+      <c r="A35" s="7" t="s">
+        <v>161</v>
       </c>
       <c r="B35" s="7" t="s">
-        <v>35</v>
+        <v>31</v>
       </c>
       <c r="C35" s="21">
         <v>9786263057036</v>
       </c>
       <c r="D35" s="20" t="s">
-        <v>33</v>
+        <v>30</v>
       </c>
       <c r="E35" s="7" t="s">
-        <v>108</v>
+        <v>101</v>
       </c>
       <c r="F35" s="4" t="s">
-        <v>168</v>
+        <v>159</v>
       </c>
       <c r="G35" s="4"/>
       <c r="H35" s="4"/>
@@ -3502,24 +3489,24 @@
       <c r="S35" s="4"/>
       <c r="T35" s="4"/>
     </row>
-    <row r="36" spans="1:22" s="5" customFormat="1" ht="34" x14ac:dyDescent="0.4">
+    <row r="36" spans="1:22" ht="34" x14ac:dyDescent="0.4">
       <c r="A36" s="7" t="s">
-        <v>34</v>
+        <v>161</v>
       </c>
       <c r="B36" s="11" t="s">
-        <v>36</v>
+        <v>32</v>
       </c>
       <c r="C36" s="10">
         <v>9789865503628</v>
       </c>
       <c r="D36" s="11" t="s">
-        <v>104</v>
+        <v>97</v>
       </c>
       <c r="E36" s="7" t="s">
-        <v>48</v>
+        <v>44</v>
       </c>
       <c r="F36" s="4" t="s">
-        <v>168</v>
+        <v>159</v>
       </c>
       <c r="G36" s="4"/>
       <c r="H36" s="4"/>
@@ -3536,24 +3523,24 @@
       <c r="S36" s="4"/>
       <c r="T36" s="4"/>
     </row>
-    <row r="37" spans="1:22" s="5" customFormat="1" ht="34" x14ac:dyDescent="0.4">
-      <c r="A37" s="6" t="s">
-        <v>34</v>
+    <row r="37" spans="1:22" ht="34" x14ac:dyDescent="0.4">
+      <c r="A37" s="7" t="s">
+        <v>161</v>
       </c>
       <c r="B37" s="11" t="s">
-        <v>37</v>
+        <v>33</v>
       </c>
       <c r="C37" s="10">
         <v>9789575709570</v>
       </c>
       <c r="D37" s="11" t="s">
-        <v>104</v>
+        <v>97</v>
       </c>
       <c r="E37" s="11" t="s">
-        <v>48</v>
+        <v>44</v>
       </c>
       <c r="F37" s="4" t="s">
-        <v>168</v>
+        <v>159</v>
       </c>
       <c r="G37" s="4"/>
       <c r="H37" s="4"/>
@@ -3570,24 +3557,24 @@
       <c r="S37" s="4"/>
       <c r="T37" s="4"/>
     </row>
-    <row r="38" spans="1:22" s="5" customFormat="1" x14ac:dyDescent="0.4">
-      <c r="A38" s="6" t="s">
+    <row r="38" spans="1:22" x14ac:dyDescent="0.4">
+      <c r="A38" s="7" t="s">
+        <v>161</v>
+      </c>
+      <c r="B38" s="22" t="s">
         <v>34</v>
-      </c>
-      <c r="B38" s="22" t="s">
-        <v>38</v>
       </c>
       <c r="C38" s="16">
         <v>9786263076488</v>
       </c>
       <c r="D38" s="6" t="s">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="E38" s="4" t="s">
-        <v>108</v>
+        <v>101</v>
       </c>
       <c r="F38" s="4" t="s">
-        <v>168</v>
+        <v>159</v>
       </c>
       <c r="G38" s="4"/>
       <c r="H38" s="4"/>
@@ -3604,24 +3591,24 @@
       <c r="S38" s="4"/>
       <c r="T38" s="4"/>
     </row>
-    <row r="39" spans="1:22" s="5" customFormat="1" x14ac:dyDescent="0.4">
-      <c r="A39" s="6" t="s">
-        <v>34</v>
+    <row r="39" spans="1:22" x14ac:dyDescent="0.4">
+      <c r="A39" s="7" t="s">
+        <v>161</v>
       </c>
       <c r="B39" s="22" t="s">
-        <v>39</v>
+        <v>35</v>
       </c>
       <c r="C39" s="16">
         <v>9786267352267</v>
       </c>
       <c r="D39" s="6" t="s">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="E39" s="4" t="s">
-        <v>108</v>
+        <v>101</v>
       </c>
       <c r="F39" s="4" t="s">
-        <v>168</v>
+        <v>159</v>
       </c>
       <c r="G39" s="4"/>
       <c r="H39" s="4"/>
@@ -3638,24 +3625,24 @@
       <c r="S39" s="4"/>
       <c r="T39" s="4"/>
     </row>
-    <row r="40" spans="1:22" s="5" customFormat="1" x14ac:dyDescent="0.4">
-      <c r="A40" s="6" t="s">
-        <v>34</v>
+    <row r="40" spans="1:22" x14ac:dyDescent="0.4">
+      <c r="A40" s="7" t="s">
+        <v>161</v>
       </c>
       <c r="B40" s="6" t="s">
-        <v>40</v>
+        <v>36</v>
       </c>
       <c r="C40" s="23">
         <v>9789571472119</v>
       </c>
       <c r="D40" s="6" t="s">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="E40" s="4" t="s">
-        <v>108</v>
+        <v>101</v>
       </c>
       <c r="F40" s="4" t="s">
-        <v>168</v>
+        <v>159</v>
       </c>
       <c r="G40" s="4"/>
       <c r="H40" s="4"/>
@@ -3672,24 +3659,24 @@
       <c r="S40" s="4"/>
       <c r="T40" s="4"/>
     </row>
-    <row r="41" spans="1:22" s="5" customFormat="1" x14ac:dyDescent="0.4">
-      <c r="A41" s="6" t="s">
-        <v>34</v>
+    <row r="41" spans="1:22" x14ac:dyDescent="0.4">
+      <c r="A41" s="7" t="s">
+        <v>161</v>
       </c>
       <c r="B41" s="6" t="s">
-        <v>41</v>
+        <v>37</v>
       </c>
       <c r="C41" s="16">
         <v>9789575035730</v>
       </c>
       <c r="D41" s="6" t="s">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="E41" s="6" t="s">
-        <v>108</v>
+        <v>101</v>
       </c>
       <c r="F41" s="4" t="s">
-        <v>168</v>
+        <v>159</v>
       </c>
       <c r="G41" s="4"/>
       <c r="H41" s="4"/>
@@ -3707,23 +3694,23 @@
       <c r="T41" s="4"/>
     </row>
     <row r="42" spans="1:22" s="27" customFormat="1" x14ac:dyDescent="0.4">
-      <c r="A42" s="6" t="s">
-        <v>34</v>
+      <c r="A42" s="7" t="s">
+        <v>161</v>
       </c>
       <c r="B42" s="24" t="s">
-        <v>129</v>
+        <v>120</v>
       </c>
       <c r="C42" s="25">
         <v>9789573246282</v>
       </c>
       <c r="D42" s="24" t="s">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="E42" s="26" t="s">
-        <v>108</v>
+        <v>101</v>
       </c>
       <c r="F42" s="4" t="s">
-        <v>168</v>
+        <v>159</v>
       </c>
       <c r="G42" s="24"/>
       <c r="H42" s="24"/>
@@ -3740,24 +3727,24 @@
       <c r="S42" s="24"/>
       <c r="T42" s="24"/>
     </row>
-    <row r="43" spans="1:22" s="5" customFormat="1" x14ac:dyDescent="0.4">
-      <c r="A43" s="6" t="s">
-        <v>34</v>
+    <row r="43" spans="1:22" x14ac:dyDescent="0.4">
+      <c r="A43" s="7" t="s">
+        <v>161</v>
       </c>
       <c r="B43" s="4" t="s">
-        <v>130</v>
+        <v>121</v>
       </c>
       <c r="C43" s="10">
         <v>9789860633900</v>
       </c>
       <c r="D43" s="6" t="s">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="E43" s="26" t="s">
-        <v>108</v>
+        <v>101</v>
       </c>
       <c r="F43" s="4" t="s">
-        <v>168</v>
+        <v>159</v>
       </c>
       <c r="G43" s="4"/>
       <c r="H43" s="4"/>
@@ -3775,23 +3762,23 @@
       <c r="T43" s="4"/>
     </row>
     <row r="44" spans="1:22" s="27" customFormat="1" x14ac:dyDescent="0.4">
-      <c r="A44" s="6" t="s">
-        <v>34</v>
+      <c r="A44" s="7" t="s">
+        <v>161</v>
       </c>
       <c r="B44" s="26" t="s">
-        <v>131</v>
+        <v>122</v>
       </c>
       <c r="C44" s="28">
         <v>9786263051508</v>
       </c>
       <c r="D44" s="24" t="s">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="E44" s="26" t="s">
-        <v>108</v>
+        <v>101</v>
       </c>
       <c r="F44" s="4" t="s">
-        <v>168</v>
+        <v>159</v>
       </c>
       <c r="G44" s="24"/>
       <c r="H44" s="24"/>
@@ -3808,24 +3795,24 @@
       <c r="S44" s="24"/>
       <c r="T44" s="24"/>
     </row>
-    <row r="45" spans="1:22" s="5" customFormat="1" x14ac:dyDescent="0.4">
-      <c r="A45" s="6" t="s">
-        <v>34</v>
+    <row r="45" spans="1:22" x14ac:dyDescent="0.4">
+      <c r="A45" s="7" t="s">
+        <v>161</v>
       </c>
       <c r="B45" s="6" t="s">
-        <v>42</v>
+        <v>38</v>
       </c>
       <c r="C45" s="23">
         <v>9789573297901</v>
       </c>
       <c r="D45" s="6" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="E45" s="6" t="s">
-        <v>108</v>
+        <v>101</v>
       </c>
       <c r="F45" s="4" t="s">
-        <v>168</v>
+        <v>159</v>
       </c>
       <c r="G45" s="4"/>
       <c r="H45" s="4"/>
@@ -3842,24 +3829,24 @@
       <c r="S45" s="4"/>
       <c r="T45" s="4"/>
     </row>
-    <row r="46" spans="1:22" s="5" customFormat="1" x14ac:dyDescent="0.4">
-      <c r="A46" s="6" t="s">
-        <v>34</v>
+    <row r="46" spans="1:22" x14ac:dyDescent="0.4">
+      <c r="A46" s="7" t="s">
+        <v>161</v>
       </c>
       <c r="B46" s="6" t="s">
-        <v>43</v>
+        <v>39</v>
       </c>
       <c r="C46" s="23">
         <v>9786267127674</v>
       </c>
       <c r="D46" s="6" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="E46" s="6" t="s">
-        <v>108</v>
+        <v>101</v>
       </c>
       <c r="F46" s="4" t="s">
-        <v>168</v>
+        <v>159</v>
       </c>
       <c r="G46" s="4"/>
       <c r="H46" s="4"/>
@@ -3877,23 +3864,23 @@
       <c r="T46" s="4"/>
     </row>
     <row r="47" spans="1:22" s="27" customFormat="1" x14ac:dyDescent="0.4">
-      <c r="A47" s="24" t="s">
-        <v>31</v>
+      <c r="A47" s="7" t="s">
+        <v>161</v>
       </c>
       <c r="B47" s="26" t="s">
-        <v>44</v>
+        <v>40</v>
       </c>
       <c r="C47" s="28">
         <v>9789864793419</v>
       </c>
       <c r="D47" s="6" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="E47" s="6" t="s">
-        <v>108</v>
+        <v>101</v>
       </c>
       <c r="F47" s="4" t="s">
-        <v>168</v>
+        <v>159</v>
       </c>
       <c r="G47" s="24"/>
       <c r="H47" s="24"/>
@@ -3911,23 +3898,23 @@
       <c r="T47" s="24"/>
     </row>
     <row r="48" spans="1:22" s="27" customFormat="1" x14ac:dyDescent="0.4">
-      <c r="A48" s="26" t="s">
-        <v>31</v>
+      <c r="A48" s="7" t="s">
+        <v>161</v>
       </c>
       <c r="B48" s="29" t="s">
-        <v>45</v>
+        <v>41</v>
       </c>
       <c r="C48" s="28">
         <v>9789865257675</v>
       </c>
       <c r="D48" s="6" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="E48" s="6" t="s">
-        <v>108</v>
+        <v>101</v>
       </c>
       <c r="F48" s="4" t="s">
-        <v>168</v>
+        <v>159</v>
       </c>
       <c r="G48" s="24"/>
       <c r="H48" s="24"/>
@@ -3945,23 +3932,23 @@
       <c r="T48" s="24"/>
     </row>
     <row r="49" spans="1:20" s="31" customFormat="1" x14ac:dyDescent="0.4">
-      <c r="A49" s="6" t="s">
-        <v>34</v>
+      <c r="A49" s="7" t="s">
+        <v>161</v>
       </c>
       <c r="B49" s="29" t="s">
-        <v>132</v>
+        <v>123</v>
       </c>
       <c r="C49" s="30">
         <v>9789869504737</v>
       </c>
       <c r="D49" s="6" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="E49" s="6" t="s">
-        <v>108</v>
+        <v>101</v>
       </c>
       <c r="F49" s="4" t="s">
-        <v>168</v>
+        <v>159</v>
       </c>
       <c r="G49" s="24"/>
       <c r="H49" s="24"/>
@@ -3979,23 +3966,23 @@
       <c r="T49" s="24"/>
     </row>
     <row r="50" spans="1:20" s="27" customFormat="1" x14ac:dyDescent="0.4">
-      <c r="A50" s="6" t="s">
-        <v>31</v>
+      <c r="A50" s="7" t="s">
+        <v>161</v>
       </c>
       <c r="B50" s="6" t="s">
-        <v>133</v>
+        <v>124</v>
       </c>
       <c r="C50" s="12">
         <v>9789865535476</v>
       </c>
       <c r="D50" s="6" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="E50" s="6" t="s">
-        <v>108</v>
+        <v>101</v>
       </c>
       <c r="F50" s="4" t="s">
-        <v>168</v>
+        <v>159</v>
       </c>
       <c r="G50" s="24"/>
       <c r="H50" s="24"/>
@@ -4013,23 +4000,23 @@
       <c r="T50" s="24"/>
     </row>
     <row r="51" spans="1:20" s="31" customFormat="1" x14ac:dyDescent="0.4">
-      <c r="A51" s="6" t="s">
-        <v>34</v>
+      <c r="A51" s="7" t="s">
+        <v>161</v>
       </c>
       <c r="B51" s="32" t="s">
-        <v>134</v>
+        <v>125</v>
       </c>
       <c r="C51" s="33">
         <v>9789579095587</v>
       </c>
       <c r="D51" s="6" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="E51" s="6" t="s">
-        <v>108</v>
+        <v>101</v>
       </c>
       <c r="F51" s="4" t="s">
-        <v>168</v>
+        <v>159</v>
       </c>
       <c r="G51" s="34"/>
       <c r="H51" s="34"/>
@@ -4047,23 +4034,23 @@
       <c r="T51" s="34"/>
     </row>
     <row r="52" spans="1:20" s="27" customFormat="1" x14ac:dyDescent="0.4">
-      <c r="A52" s="6" t="s">
-        <v>34</v>
+      <c r="A52" s="7" t="s">
+        <v>161</v>
       </c>
       <c r="B52" s="29" t="s">
-        <v>46</v>
+        <v>42</v>
       </c>
       <c r="C52" s="35">
         <v>9786263056244</v>
       </c>
       <c r="D52" s="24" t="s">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="E52" s="4" t="s">
-        <v>108</v>
+        <v>101</v>
       </c>
       <c r="F52" s="4" t="s">
-        <v>168</v>
+        <v>159</v>
       </c>
       <c r="G52" s="24"/>
       <c r="H52" s="24"/>
@@ -4080,24 +4067,24 @@
       <c r="S52" s="24"/>
       <c r="T52" s="24"/>
     </row>
-    <row r="53" spans="1:20" s="5" customFormat="1" x14ac:dyDescent="0.4">
-      <c r="A53" s="6" t="s">
-        <v>34</v>
+    <row r="53" spans="1:20" x14ac:dyDescent="0.4">
+      <c r="A53" s="7" t="s">
+        <v>161</v>
       </c>
       <c r="B53" s="5" t="s">
-        <v>47</v>
+        <v>43</v>
       </c>
       <c r="C53" s="10">
         <v>9789861899992</v>
       </c>
       <c r="D53" s="5" t="s">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="E53" s="36" t="s">
-        <v>48</v>
+        <v>44</v>
       </c>
       <c r="F53" s="4" t="s">
-        <v>168</v>
+        <v>159</v>
       </c>
       <c r="G53" s="4"/>
       <c r="H53" s="4"/>
@@ -4115,23 +4102,23 @@
       <c r="T53" s="4"/>
     </row>
     <row r="54" spans="1:20" s="27" customFormat="1" x14ac:dyDescent="0.4">
-      <c r="A54" s="24" t="s">
-        <v>31</v>
+      <c r="A54" s="7" t="s">
+        <v>161</v>
       </c>
       <c r="B54" s="24" t="s">
-        <v>135</v>
+        <v>126</v>
       </c>
       <c r="C54" s="25">
         <v>9789865253080</v>
       </c>
       <c r="D54" s="24" t="s">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="E54" s="34" t="s">
-        <v>108</v>
+        <v>101</v>
       </c>
       <c r="F54" s="4" t="s">
-        <v>168</v>
+        <v>159</v>
       </c>
       <c r="G54" s="24"/>
       <c r="H54" s="24"/>
@@ -4148,24 +4135,24 @@
       <c r="S54" s="24"/>
       <c r="T54" s="24"/>
     </row>
-    <row r="55" spans="1:20" s="5" customFormat="1" x14ac:dyDescent="0.4">
-      <c r="A55" s="6" t="s">
-        <v>34</v>
+    <row r="55" spans="1:20" x14ac:dyDescent="0.4">
+      <c r="A55" s="7" t="s">
+        <v>161</v>
       </c>
       <c r="B55" s="4" t="s">
-        <v>136</v>
+        <v>127</v>
       </c>
       <c r="C55" s="12">
         <v>9789863429814</v>
       </c>
       <c r="D55" s="4" t="s">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="E55" s="34" t="s">
-        <v>108</v>
+        <v>101</v>
       </c>
       <c r="F55" s="4" t="s">
-        <v>168</v>
+        <v>159</v>
       </c>
       <c r="G55" s="4"/>
       <c r="H55" s="4"/>
@@ -4183,23 +4170,23 @@
       <c r="T55" s="4"/>
     </row>
     <row r="56" spans="1:20" s="38" customFormat="1" x14ac:dyDescent="0.4">
-      <c r="A56" s="6" t="s">
-        <v>34</v>
+      <c r="A56" s="7" t="s">
+        <v>161</v>
       </c>
       <c r="B56" s="26" t="s">
-        <v>137</v>
+        <v>128</v>
       </c>
       <c r="C56" s="25">
         <v>9789573295433</v>
       </c>
       <c r="D56" s="26" t="s">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="E56" s="26" t="s">
-        <v>48</v>
+        <v>44</v>
       </c>
       <c r="F56" s="4" t="s">
-        <v>168</v>
+        <v>159</v>
       </c>
       <c r="G56" s="37"/>
       <c r="H56" s="37"/>
@@ -4217,23 +4204,23 @@
       <c r="T56" s="37"/>
     </row>
     <row r="57" spans="1:20" s="38" customFormat="1" x14ac:dyDescent="0.4">
-      <c r="A57" s="6" t="s">
-        <v>34</v>
+      <c r="A57" s="7" t="s">
+        <v>161</v>
       </c>
       <c r="B57" s="26" t="s">
-        <v>138</v>
+        <v>129</v>
       </c>
       <c r="C57" s="25">
         <v>4711132385519</v>
       </c>
       <c r="D57" s="26" t="s">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="E57" s="26" t="s">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="F57" s="4" t="s">
-        <v>168</v>
+        <v>159</v>
       </c>
       <c r="G57" s="37"/>
       <c r="H57" s="37"/>
@@ -4250,64 +4237,64 @@
       <c r="S57" s="37"/>
       <c r="T57" s="37"/>
     </row>
-    <row r="58" spans="1:20" s="5" customFormat="1" ht="34" x14ac:dyDescent="0.4">
+    <row r="58" spans="1:20" ht="34" x14ac:dyDescent="0.4">
       <c r="A58" s="7" t="s">
-        <v>109</v>
+        <v>162</v>
       </c>
       <c r="B58" s="7" t="s">
-        <v>50</v>
+        <v>46</v>
       </c>
       <c r="C58" s="10">
         <v>9789573277583</v>
       </c>
       <c r="D58" s="9" t="s">
-        <v>110</v>
+        <v>102</v>
       </c>
       <c r="E58" s="11" t="s">
-        <v>51</v>
+        <v>47</v>
       </c>
       <c r="F58" s="4" t="s">
-        <v>168</v>
-      </c>
-    </row>
-    <row r="59" spans="1:20" s="5" customFormat="1" ht="34" x14ac:dyDescent="0.4">
+        <v>159</v>
+      </c>
+    </row>
+    <row r="59" spans="1:20" ht="34" x14ac:dyDescent="0.4">
       <c r="A59" s="7" t="s">
-        <v>57</v>
+        <v>162</v>
       </c>
       <c r="B59" s="11" t="s">
-        <v>52</v>
+        <v>48</v>
       </c>
       <c r="C59" s="10">
         <v>9789869504799</v>
       </c>
       <c r="D59" s="20" t="s">
-        <v>104</v>
+        <v>97</v>
       </c>
       <c r="E59" s="11" t="s">
-        <v>51</v>
+        <v>47</v>
       </c>
       <c r="F59" s="4" t="s">
-        <v>168</v>
-      </c>
-    </row>
-    <row r="60" spans="1:20" s="5" customFormat="1" ht="34" x14ac:dyDescent="0.4">
+        <v>159</v>
+      </c>
+    </row>
+    <row r="60" spans="1:20" ht="34" x14ac:dyDescent="0.4">
       <c r="A60" s="7" t="s">
-        <v>57</v>
+        <v>162</v>
       </c>
       <c r="B60" s="7" t="s">
-        <v>53</v>
+        <v>49</v>
       </c>
       <c r="C60" s="10">
         <v>9786267281376</v>
       </c>
       <c r="D60" s="20" t="s">
-        <v>111</v>
+        <v>103</v>
       </c>
       <c r="E60" s="7" t="s">
-        <v>48</v>
+        <v>44</v>
       </c>
       <c r="F60" s="4" t="s">
-        <v>168</v>
+        <v>159</v>
       </c>
       <c r="G60" s="4"/>
       <c r="H60" s="4"/>
@@ -4324,124 +4311,124 @@
       <c r="S60" s="4"/>
       <c r="T60" s="4"/>
     </row>
-    <row r="61" spans="1:20" s="5" customFormat="1" ht="34" x14ac:dyDescent="0.4">
+    <row r="61" spans="1:20" ht="34" x14ac:dyDescent="0.4">
       <c r="A61" s="7" t="s">
-        <v>57</v>
+        <v>162</v>
       </c>
       <c r="B61" s="11" t="s">
-        <v>116</v>
+        <v>107</v>
       </c>
       <c r="C61" s="10">
         <v>9786269583263</v>
       </c>
       <c r="D61" s="11" t="s">
-        <v>111</v>
+        <v>103</v>
       </c>
       <c r="E61" s="7" t="s">
-        <v>71</v>
+        <v>65</v>
       </c>
       <c r="F61" s="4" t="s">
-        <v>168</v>
-      </c>
-    </row>
-    <row r="62" spans="1:20" s="5" customFormat="1" ht="34" x14ac:dyDescent="0.4">
+        <v>159</v>
+      </c>
+    </row>
+    <row r="62" spans="1:20" ht="34" x14ac:dyDescent="0.4">
       <c r="A62" s="7" t="s">
-        <v>57</v>
+        <v>162</v>
       </c>
       <c r="B62" s="6" t="s">
-        <v>117</v>
+        <v>108</v>
       </c>
       <c r="C62" s="23">
         <v>9789865257149</v>
       </c>
       <c r="D62" s="11" t="s">
-        <v>111</v>
+        <v>103</v>
       </c>
       <c r="E62" s="4" t="s">
-        <v>49</v>
+        <v>45</v>
       </c>
       <c r="F62" s="4" t="s">
-        <v>168</v>
-      </c>
-    </row>
-    <row r="63" spans="1:20" s="5" customFormat="1" ht="34" x14ac:dyDescent="0.4">
+        <v>159</v>
+      </c>
+    </row>
+    <row r="63" spans="1:20" ht="34" x14ac:dyDescent="0.4">
       <c r="A63" s="7" t="s">
-        <v>57</v>
+        <v>162</v>
       </c>
       <c r="B63" s="7" t="s">
-        <v>118</v>
+        <v>109</v>
       </c>
       <c r="C63" s="23">
         <v>9789861776446</v>
       </c>
       <c r="D63" s="9" t="s">
-        <v>110</v>
+        <v>102</v>
       </c>
       <c r="E63" s="7" t="s">
-        <v>54</v>
+        <v>50</v>
       </c>
       <c r="F63" s="4" t="s">
-        <v>168</v>
-      </c>
-    </row>
-    <row r="64" spans="1:20" s="5" customFormat="1" x14ac:dyDescent="0.4">
+        <v>159</v>
+      </c>
+    </row>
+    <row r="64" spans="1:20" x14ac:dyDescent="0.4">
       <c r="A64" s="7" t="s">
-        <v>57</v>
+        <v>162</v>
       </c>
       <c r="B64" s="4" t="s">
-        <v>55</v>
+        <v>51</v>
       </c>
       <c r="C64" s="12">
         <v>9789864775477</v>
       </c>
       <c r="D64" s="11" t="s">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="E64" s="4" t="s">
-        <v>54</v>
+        <v>50</v>
       </c>
       <c r="F64" s="4" t="s">
-        <v>168</v>
-      </c>
-    </row>
-    <row r="65" spans="1:20" s="5" customFormat="1" x14ac:dyDescent="0.4">
+        <v>159</v>
+      </c>
+    </row>
+    <row r="65" spans="1:20" x14ac:dyDescent="0.4">
       <c r="A65" s="7" t="s">
-        <v>57</v>
+        <v>162</v>
       </c>
       <c r="B65" s="4" t="s">
-        <v>56</v>
+        <v>52</v>
       </c>
       <c r="C65" s="12">
         <v>9789576868177</v>
       </c>
       <c r="D65" s="11" t="s">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="E65" s="4" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="F65" s="4" t="s">
-        <v>168</v>
-      </c>
-    </row>
-    <row r="66" spans="1:20" s="5" customFormat="1" x14ac:dyDescent="0.4">
-      <c r="A66" s="4" t="s">
-        <v>57</v>
+        <v>159</v>
+      </c>
+    </row>
+    <row r="66" spans="1:20" x14ac:dyDescent="0.4">
+      <c r="A66" s="7" t="s">
+        <v>162</v>
       </c>
       <c r="B66" s="39" t="s">
-        <v>58</v>
+        <v>53</v>
       </c>
       <c r="C66" s="23">
         <v>9786263292765</v>
       </c>
       <c r="D66" s="11" t="s">
-        <v>59</v>
+        <v>54</v>
       </c>
       <c r="E66" s="11" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="F66" s="4" t="s">
-        <v>168</v>
+        <v>159</v>
       </c>
       <c r="G66" s="4"/>
       <c r="H66" s="4"/>
@@ -4458,106 +4445,106 @@
       <c r="S66" s="6"/>
       <c r="T66" s="6"/>
     </row>
-    <row r="67" spans="1:20" s="5" customFormat="1" x14ac:dyDescent="0.4">
-      <c r="A67" s="6" t="s">
-        <v>57</v>
+    <row r="67" spans="1:20" x14ac:dyDescent="0.4">
+      <c r="A67" s="7" t="s">
+        <v>162</v>
       </c>
       <c r="B67" s="4" t="s">
-        <v>119</v>
+        <v>110</v>
       </c>
       <c r="C67" s="12">
         <v>9789571471952</v>
       </c>
       <c r="D67" s="4" t="s">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="E67" s="6" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="F67" s="4" t="s">
-        <v>168</v>
+        <v>159</v>
       </c>
     </row>
     <row r="68" spans="1:20" s="4" customFormat="1" x14ac:dyDescent="0.4">
-      <c r="A68" s="6" t="s">
-        <v>57</v>
+      <c r="A68" s="7" t="s">
+        <v>162</v>
       </c>
       <c r="B68" s="22" t="s">
-        <v>120</v>
+        <v>111</v>
       </c>
       <c r="C68" s="16">
         <v>9789576582950</v>
       </c>
       <c r="D68" s="6" t="s">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="E68" s="11" t="s">
-        <v>51</v>
+        <v>47</v>
       </c>
       <c r="F68" s="4" t="s">
-        <v>168</v>
+        <v>159</v>
       </c>
     </row>
     <row r="69" spans="1:20" s="4" customFormat="1" x14ac:dyDescent="0.4">
-      <c r="A69" s="6" t="s">
-        <v>57</v>
+      <c r="A69" s="7" t="s">
+        <v>162</v>
       </c>
       <c r="B69" s="22" t="s">
-        <v>121</v>
+        <v>112</v>
       </c>
       <c r="C69" s="16">
         <v>9789576582134</v>
       </c>
       <c r="D69" s="6" t="s">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="E69" s="6" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="F69" s="4" t="s">
-        <v>168</v>
-      </c>
-    </row>
-    <row r="70" spans="1:20" s="5" customFormat="1" x14ac:dyDescent="0.4">
-      <c r="A70" s="6" t="s">
-        <v>109</v>
+        <v>159</v>
+      </c>
+    </row>
+    <row r="70" spans="1:20" x14ac:dyDescent="0.4">
+      <c r="A70" s="7" t="s">
+        <v>162</v>
       </c>
       <c r="B70" s="6" t="s">
-        <v>61</v>
+        <v>56</v>
       </c>
       <c r="C70" s="23">
         <v>9789579095464</v>
       </c>
       <c r="D70" s="6" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="E70" s="6" t="s">
-        <v>54</v>
+        <v>50</v>
       </c>
       <c r="F70" s="4" t="s">
-        <v>168</v>
+        <v>159</v>
       </c>
       <c r="G70" s="4"/>
       <c r="H70" s="4"/>
     </row>
-    <row r="71" spans="1:20" s="5" customFormat="1" x14ac:dyDescent="0.4">
-      <c r="A71" s="6" t="s">
+    <row r="71" spans="1:20" x14ac:dyDescent="0.4">
+      <c r="A71" s="7" t="s">
+        <v>162</v>
+      </c>
+      <c r="B71" s="39" t="s">
         <v>57</v>
-      </c>
-      <c r="B71" s="39" t="s">
-        <v>62</v>
       </c>
       <c r="C71" s="23">
         <v>9789864505944</v>
       </c>
       <c r="D71" s="17" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="E71" s="39" t="s">
-        <v>49</v>
+        <v>45</v>
       </c>
       <c r="F71" s="4" t="s">
-        <v>168</v>
+        <v>159</v>
       </c>
       <c r="G71" s="4"/>
       <c r="H71" s="4"/>
@@ -4574,125 +4561,125 @@
       <c r="S71" s="4"/>
       <c r="T71" s="4"/>
     </row>
-    <row r="72" spans="1:20" s="5" customFormat="1" x14ac:dyDescent="0.4">
-      <c r="A72" s="6" t="s">
-        <v>57</v>
+    <row r="72" spans="1:20" x14ac:dyDescent="0.4">
+      <c r="A72" s="7" t="s">
+        <v>162</v>
       </c>
       <c r="B72" s="6" t="s">
-        <v>63</v>
+        <v>58</v>
       </c>
       <c r="C72" s="16">
         <v>9786267043219</v>
       </c>
       <c r="D72" s="11" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="E72" s="6" t="s">
-        <v>51</v>
+        <v>47</v>
       </c>
       <c r="F72" s="4" t="s">
-        <v>168</v>
-      </c>
-    </row>
-    <row r="73" spans="1:20" s="5" customFormat="1" x14ac:dyDescent="0.4">
-      <c r="A73" s="6" t="s">
-        <v>57</v>
+        <v>159</v>
+      </c>
+    </row>
+    <row r="73" spans="1:20" x14ac:dyDescent="0.4">
+      <c r="A73" s="7" t="s">
+        <v>162</v>
       </c>
       <c r="B73" s="6" t="s">
-        <v>122</v>
+        <v>113</v>
       </c>
       <c r="C73" s="16">
         <v>9789578544468</v>
       </c>
       <c r="D73" s="17" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="E73" s="6" t="s">
-        <v>51</v>
+        <v>47</v>
       </c>
       <c r="F73" s="4" t="s">
-        <v>168</v>
+        <v>159</v>
       </c>
       <c r="G73" s="4"/>
     </row>
-    <row r="74" spans="1:20" s="5" customFormat="1" x14ac:dyDescent="0.4">
-      <c r="A74" s="6" t="s">
-        <v>57</v>
+    <row r="74" spans="1:20" x14ac:dyDescent="0.4">
+      <c r="A74" s="7" t="s">
+        <v>162</v>
       </c>
       <c r="B74" s="6" t="s">
-        <v>123</v>
+        <v>114</v>
       </c>
       <c r="C74" s="16">
         <v>9789576583711</v>
       </c>
       <c r="D74" s="17" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="E74" s="6" t="s">
-        <v>49</v>
+        <v>45</v>
       </c>
       <c r="F74" s="4" t="s">
-        <v>168</v>
-      </c>
-    </row>
-    <row r="75" spans="1:20" s="5" customFormat="1" x14ac:dyDescent="0.4">
-      <c r="A75" s="6" t="s">
-        <v>57</v>
+        <v>159</v>
+      </c>
+    </row>
+    <row r="75" spans="1:20" x14ac:dyDescent="0.4">
+      <c r="A75" s="7" t="s">
+        <v>162</v>
       </c>
       <c r="B75" s="6" t="s">
-        <v>124</v>
+        <v>115</v>
       </c>
       <c r="C75" s="16">
         <v>9789864505845</v>
       </c>
       <c r="D75" s="17" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="E75" s="6" t="s">
-        <v>54</v>
+        <v>50</v>
       </c>
       <c r="F75" s="4" t="s">
-        <v>168</v>
-      </c>
-    </row>
-    <row r="76" spans="1:20" s="5" customFormat="1" x14ac:dyDescent="0.4">
-      <c r="A76" s="6" t="s">
-        <v>112</v>
+        <v>159</v>
+      </c>
+    </row>
+    <row r="76" spans="1:20" x14ac:dyDescent="0.4">
+      <c r="A76" s="7" t="s">
+        <v>162</v>
       </c>
       <c r="B76" s="5" t="s">
-        <v>64</v>
+        <v>59</v>
       </c>
       <c r="C76" s="12">
         <v>9789570854183</v>
       </c>
       <c r="D76" s="5" t="s">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="E76" s="5" t="s">
-        <v>49</v>
+        <v>45</v>
       </c>
       <c r="F76" s="4" t="s">
-        <v>168</v>
-      </c>
-    </row>
-    <row r="77" spans="1:20" s="5" customFormat="1" x14ac:dyDescent="0.4">
-      <c r="A77" s="4" t="s">
-        <v>57</v>
+        <v>159</v>
+      </c>
+    </row>
+    <row r="77" spans="1:20" x14ac:dyDescent="0.4">
+      <c r="A77" s="7" t="s">
+        <v>162</v>
       </c>
       <c r="B77" s="7" t="s">
-        <v>65</v>
+        <v>60</v>
       </c>
       <c r="C77" s="21">
         <v>9789869483759</v>
       </c>
       <c r="D77" s="9" t="s">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="E77" s="7" t="s">
-        <v>51</v>
+        <v>47</v>
       </c>
       <c r="F77" s="4" t="s">
-        <v>168</v>
+        <v>159</v>
       </c>
       <c r="G77" s="4"/>
       <c r="H77" s="4"/>
@@ -4709,24 +4696,24 @@
       <c r="S77" s="6"/>
       <c r="T77" s="6"/>
     </row>
-    <row r="78" spans="1:20" s="5" customFormat="1" x14ac:dyDescent="0.4">
-      <c r="A78" s="4" t="s">
-        <v>57</v>
+    <row r="78" spans="1:20" x14ac:dyDescent="0.4">
+      <c r="A78" s="7" t="s">
+        <v>162</v>
       </c>
       <c r="B78" s="6" t="s">
-        <v>125</v>
+        <v>116</v>
       </c>
       <c r="C78" s="23">
         <v>9789867630148</v>
       </c>
       <c r="D78" s="6" t="s">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="E78" s="40" t="s">
-        <v>71</v>
+        <v>65</v>
       </c>
       <c r="F78" s="4" t="s">
-        <v>168</v>
+        <v>159</v>
       </c>
       <c r="G78" s="4"/>
       <c r="H78" s="4"/>
@@ -4743,224 +4730,224 @@
       <c r="S78" s="6"/>
       <c r="T78" s="6"/>
     </row>
-    <row r="79" spans="1:20" s="5" customFormat="1" ht="34" x14ac:dyDescent="0.4">
-      <c r="A79" s="4" t="s">
-        <v>57</v>
+    <row r="79" spans="1:20" ht="34" x14ac:dyDescent="0.4">
+      <c r="A79" s="7" t="s">
+        <v>162</v>
       </c>
       <c r="B79" s="22" t="s">
-        <v>126</v>
+        <v>117</v>
       </c>
       <c r="C79" s="16">
         <v>9786263050174</v>
       </c>
       <c r="D79" s="6" t="s">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="E79" s="6" t="s">
-        <v>54</v>
+        <v>50</v>
       </c>
       <c r="F79" s="4" t="s">
-        <v>168</v>
-      </c>
-    </row>
-    <row r="80" spans="1:20" s="5" customFormat="1" x14ac:dyDescent="0.4">
-      <c r="A80" s="4" t="s">
-        <v>57</v>
+        <v>159</v>
+      </c>
+    </row>
+    <row r="80" spans="1:20" x14ac:dyDescent="0.4">
+      <c r="A80" s="7" t="s">
+        <v>162</v>
       </c>
       <c r="B80" s="22" t="s">
-        <v>127</v>
+        <v>118</v>
       </c>
       <c r="C80" s="16">
         <v>9789577518774</v>
       </c>
       <c r="D80" s="6" t="s">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="E80" s="6" t="s">
-        <v>51</v>
+        <v>47</v>
       </c>
       <c r="F80" s="4" t="s">
-        <v>168</v>
-      </c>
-    </row>
-    <row r="81" spans="1:22" s="5" customFormat="1" ht="34" x14ac:dyDescent="0.4">
-      <c r="A81" s="4" t="s">
-        <v>57</v>
+        <v>159</v>
+      </c>
+    </row>
+    <row r="81" spans="1:22" ht="34" x14ac:dyDescent="0.4">
+      <c r="A81" s="7" t="s">
+        <v>162</v>
       </c>
       <c r="B81" s="22" t="s">
-        <v>128</v>
+        <v>119</v>
       </c>
       <c r="C81" s="16">
         <v>9786263580770</v>
       </c>
       <c r="D81" s="6" t="s">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="E81" s="6" t="s">
-        <v>54</v>
+        <v>50</v>
       </c>
       <c r="F81" s="4" t="s">
-        <v>168</v>
+        <v>159</v>
       </c>
     </row>
     <row r="82" spans="1:22" s="4" customFormat="1" ht="34" x14ac:dyDescent="0.4">
       <c r="A82" s="4" t="s">
-        <v>66</v>
+        <v>163</v>
       </c>
       <c r="B82" s="34" t="s">
-        <v>67</v>
+        <v>61</v>
       </c>
       <c r="C82" s="33">
         <v>9789574905027</v>
       </c>
       <c r="D82" s="22" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="E82" s="34" t="s">
-        <v>51</v>
+        <v>47</v>
       </c>
       <c r="F82" s="4" t="s">
-        <v>168</v>
+        <v>159</v>
       </c>
     </row>
     <row r="83" spans="1:22" s="4" customFormat="1" ht="34" x14ac:dyDescent="0.4">
       <c r="A83" s="4" t="s">
-        <v>66</v>
+        <v>163</v>
       </c>
       <c r="B83" s="6" t="s">
-        <v>68</v>
+        <v>62</v>
       </c>
       <c r="C83" s="16">
         <v>9789869805049</v>
       </c>
       <c r="D83" s="22" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="E83" s="6" t="s">
-        <v>51</v>
+        <v>47</v>
       </c>
       <c r="F83" s="4" t="s">
-        <v>168</v>
+        <v>159</v>
       </c>
     </row>
     <row r="84" spans="1:22" s="4" customFormat="1" ht="34" x14ac:dyDescent="0.4">
       <c r="A84" s="4" t="s">
-        <v>66</v>
+        <v>163</v>
       </c>
       <c r="B84" s="6" t="s">
-        <v>69</v>
+        <v>63</v>
       </c>
       <c r="C84" s="23">
         <v>9789576587399</v>
       </c>
       <c r="D84" s="11" t="s">
-        <v>70</v>
+        <v>64</v>
       </c>
       <c r="E84" s="6" t="s">
-        <v>51</v>
+        <v>47</v>
       </c>
       <c r="F84" s="4" t="s">
-        <v>168</v>
+        <v>159</v>
       </c>
     </row>
     <row r="85" spans="1:22" s="4" customFormat="1" ht="34" x14ac:dyDescent="0.4">
       <c r="A85" s="4" t="s">
+        <v>163</v>
+      </c>
+      <c r="B85" s="11" t="s">
         <v>66</v>
-      </c>
-      <c r="B85" s="11" t="s">
-        <v>72</v>
       </c>
       <c r="C85" s="10">
         <v>9789865060022</v>
       </c>
       <c r="D85" s="22" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="E85" s="11" t="s">
-        <v>51</v>
+        <v>47</v>
       </c>
       <c r="F85" s="4" t="s">
-        <v>168</v>
+        <v>159</v>
       </c>
     </row>
     <row r="86" spans="1:22" s="4" customFormat="1" x14ac:dyDescent="0.4">
-      <c r="A86" s="22" t="s">
-        <v>66</v>
+      <c r="A86" s="4" t="s">
+        <v>163</v>
       </c>
       <c r="B86" s="22" t="s">
-        <v>73</v>
+        <v>67</v>
       </c>
       <c r="C86" s="16">
         <v>9789860680355</v>
       </c>
       <c r="D86" s="22" t="s">
-        <v>74</v>
+        <v>68</v>
       </c>
       <c r="E86" s="22" t="s">
-        <v>51</v>
+        <v>47</v>
       </c>
       <c r="F86" s="4" t="s">
-        <v>168</v>
+        <v>159</v>
       </c>
     </row>
     <row r="87" spans="1:22" s="4" customFormat="1" x14ac:dyDescent="0.4">
-      <c r="A87" s="22" t="s">
-        <v>66</v>
+      <c r="A87" s="4" t="s">
+        <v>163</v>
       </c>
       <c r="B87" s="6" t="s">
-        <v>75</v>
+        <v>69</v>
       </c>
       <c r="C87" s="16">
         <v>9789869458276</v>
       </c>
       <c r="D87" s="6" t="s">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="E87" s="6" t="s">
-        <v>51</v>
+        <v>47</v>
       </c>
       <c r="F87" s="4" t="s">
-        <v>168</v>
+        <v>159</v>
       </c>
     </row>
     <row r="88" spans="1:22" s="4" customFormat="1" x14ac:dyDescent="0.4">
-      <c r="A88" s="6" t="s">
-        <v>66</v>
+      <c r="A88" s="4" t="s">
+        <v>163</v>
       </c>
       <c r="B88" s="6" t="s">
-        <v>76</v>
+        <v>70</v>
       </c>
       <c r="C88" s="16">
         <v>9789862894743</v>
       </c>
       <c r="D88" s="16" t="s">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="E88" s="16" t="s">
-        <v>60</v>
+        <v>55</v>
       </c>
       <c r="F88" s="4" t="s">
-        <v>168</v>
+        <v>159</v>
       </c>
     </row>
     <row r="89" spans="1:22" s="4" customFormat="1" x14ac:dyDescent="0.4">
-      <c r="A89" s="22" t="s">
-        <v>66</v>
+      <c r="A89" s="4" t="s">
+        <v>163</v>
       </c>
       <c r="B89" s="41" t="s">
-        <v>77</v>
+        <v>71</v>
       </c>
       <c r="C89" s="42">
         <v>9789864790784</v>
       </c>
       <c r="D89" s="41" t="s">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="E89" s="41" t="s">
-        <v>51</v>
+        <v>47</v>
       </c>
       <c r="F89" s="4" t="s">
-        <v>168</v>
+        <v>159</v>
       </c>
       <c r="G89" s="43"/>
       <c r="H89" s="43"/>
@@ -4980,103 +4967,103 @@
       <c r="V89" s="43"/>
     </row>
     <row r="90" spans="1:22" s="4" customFormat="1" x14ac:dyDescent="0.4">
-      <c r="A90" s="7" t="s">
-        <v>66</v>
+      <c r="A90" s="4" t="s">
+        <v>163</v>
       </c>
       <c r="B90" s="6" t="s">
-        <v>78</v>
+        <v>72</v>
       </c>
       <c r="C90" s="23">
         <v>9789869148559</v>
       </c>
       <c r="D90" s="17" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="E90" s="4" t="s">
-        <v>71</v>
+        <v>65</v>
       </c>
       <c r="F90" s="4" t="s">
-        <v>168</v>
+        <v>159</v>
       </c>
     </row>
     <row r="91" spans="1:22" s="4" customFormat="1" x14ac:dyDescent="0.4">
-      <c r="A91" s="7" t="s">
-        <v>66</v>
+      <c r="A91" s="4" t="s">
+        <v>163</v>
       </c>
       <c r="B91" s="6" t="s">
-        <v>80</v>
+        <v>74</v>
       </c>
       <c r="C91" s="23">
         <v>9789573332770</v>
       </c>
       <c r="D91" s="4" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="E91" s="4" t="s">
-        <v>79</v>
+        <v>73</v>
       </c>
       <c r="F91" s="4" t="s">
-        <v>168</v>
+        <v>159</v>
       </c>
     </row>
     <row r="92" spans="1:22" s="4" customFormat="1" x14ac:dyDescent="0.4">
-      <c r="A92" s="7" t="s">
-        <v>66</v>
+      <c r="A92" s="4" t="s">
+        <v>163</v>
       </c>
       <c r="B92" s="44" t="s">
-        <v>81</v>
+        <v>75</v>
       </c>
       <c r="C92" s="45">
         <v>9786263053151</v>
       </c>
       <c r="D92" s="34" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="E92" s="40" t="s">
-        <v>82</v>
+        <v>76</v>
       </c>
       <c r="F92" s="4" t="s">
-        <v>168</v>
+        <v>159</v>
       </c>
     </row>
     <row r="93" spans="1:22" s="4" customFormat="1" x14ac:dyDescent="0.4">
-      <c r="A93" s="7" t="s">
-        <v>66</v>
+      <c r="A93" s="4" t="s">
+        <v>163</v>
       </c>
       <c r="B93" s="6" t="s">
-        <v>83</v>
+        <v>77</v>
       </c>
       <c r="C93" s="46">
         <v>9789869319249</v>
       </c>
       <c r="D93" s="34" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="E93" s="6" t="s">
-        <v>82</v>
+        <v>76</v>
       </c>
       <c r="F93" s="4" t="s">
-        <v>168</v>
+        <v>159</v>
       </c>
     </row>
     <row r="94" spans="1:22" s="37" customFormat="1" x14ac:dyDescent="0.4">
-      <c r="A94" s="6" t="s">
-        <v>66</v>
+      <c r="A94" s="4" t="s">
+        <v>163</v>
       </c>
       <c r="B94" s="6" t="s">
-        <v>84</v>
+        <v>78</v>
       </c>
       <c r="C94" s="16">
         <v>9786269649501</v>
       </c>
       <c r="D94" s="6" t="s">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="E94" s="6" t="s">
-        <v>51</v>
+        <v>47</v>
       </c>
       <c r="F94" s="4" t="s">
-        <v>168</v>
+        <v>159</v>
       </c>
       <c r="G94" s="40"/>
       <c r="H94" s="40"/>
@@ -5096,63 +5083,63 @@
       <c r="V94" s="40"/>
     </row>
     <row r="95" spans="1:22" s="4" customFormat="1" ht="34" x14ac:dyDescent="0.4">
-      <c r="A95" s="6" t="s">
-        <v>66</v>
+      <c r="A95" s="4" t="s">
+        <v>163</v>
       </c>
       <c r="B95" s="11" t="s">
-        <v>85</v>
+        <v>79</v>
       </c>
       <c r="C95" s="10">
         <v>9786263537033</v>
       </c>
       <c r="D95" s="4" t="s">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="E95" s="40" t="s">
-        <v>82</v>
+        <v>76</v>
       </c>
       <c r="F95" s="4" t="s">
-        <v>168</v>
+        <v>159</v>
       </c>
     </row>
     <row r="96" spans="1:22" s="4" customFormat="1" x14ac:dyDescent="0.4">
-      <c r="A96" s="6" t="s">
-        <v>66</v>
+      <c r="A96" s="4" t="s">
+        <v>163</v>
       </c>
       <c r="B96" s="6" t="s">
-        <v>86</v>
+        <v>80</v>
       </c>
       <c r="C96" s="23">
         <v>9789573332763</v>
       </c>
       <c r="D96" s="4" t="s">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="E96" s="4" t="s">
-        <v>71</v>
+        <v>65</v>
       </c>
       <c r="F96" s="4" t="s">
-        <v>168</v>
+        <v>159</v>
       </c>
     </row>
     <row r="97" spans="1:22" s="37" customFormat="1" x14ac:dyDescent="0.4">
-      <c r="A97" s="6" t="s">
-        <v>66</v>
+      <c r="A97" s="4" t="s">
+        <v>163</v>
       </c>
       <c r="B97" s="6" t="s">
-        <v>87</v>
+        <v>81</v>
       </c>
       <c r="C97" s="16">
         <v>9789577518767</v>
       </c>
       <c r="D97" s="6" t="s">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="E97" s="6" t="s">
-        <v>51</v>
+        <v>47</v>
       </c>
       <c r="F97" s="4" t="s">
-        <v>168</v>
+        <v>159</v>
       </c>
       <c r="G97" s="40"/>
       <c r="H97" s="40"/>
@@ -5171,24 +5158,24 @@
       <c r="U97" s="40"/>
       <c r="V97" s="40"/>
     </row>
-    <row r="98" spans="1:22" s="5" customFormat="1" ht="34" x14ac:dyDescent="0.4">
+    <row r="98" spans="1:22" ht="34" x14ac:dyDescent="0.4">
       <c r="A98" s="47" t="s">
-        <v>90</v>
+        <v>164</v>
       </c>
       <c r="B98" s="47" t="s">
-        <v>88</v>
+        <v>82</v>
       </c>
       <c r="C98" s="12">
         <v>9786263105355</v>
       </c>
       <c r="D98" s="48" t="s">
-        <v>105</v>
+        <v>98</v>
       </c>
       <c r="E98" s="47" t="s">
-        <v>79</v>
+        <v>73</v>
       </c>
       <c r="F98" s="4" t="s">
-        <v>168</v>
+        <v>159</v>
       </c>
       <c r="G98" s="4"/>
       <c r="H98" s="4"/>
@@ -5207,24 +5194,24 @@
       <c r="U98" s="4"/>
       <c r="V98" s="4"/>
     </row>
-    <row r="99" spans="1:22" s="5" customFormat="1" ht="34" x14ac:dyDescent="0.4">
+    <row r="99" spans="1:22" ht="34" x14ac:dyDescent="0.4">
       <c r="A99" s="47" t="s">
-        <v>90</v>
+        <v>164</v>
       </c>
       <c r="B99" s="47" t="s">
-        <v>89</v>
+        <v>83</v>
       </c>
       <c r="C99" s="12">
         <v>9789571348407</v>
       </c>
       <c r="D99" s="48" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="E99" s="47" t="s">
-        <v>71</v>
+        <v>65</v>
       </c>
       <c r="F99" s="4" t="s">
-        <v>168</v>
+        <v>159</v>
       </c>
       <c r="G99" s="4"/>
       <c r="H99" s="4"/>
@@ -5243,24 +5230,24 @@
       <c r="U99" s="4"/>
       <c r="V99" s="4"/>
     </row>
-    <row r="100" spans="1:22" s="5" customFormat="1" ht="34" x14ac:dyDescent="0.4">
-      <c r="A100" s="39" t="s">
-        <v>90</v>
+    <row r="100" spans="1:22" ht="34" x14ac:dyDescent="0.4">
+      <c r="A100" s="47" t="s">
+        <v>164</v>
       </c>
       <c r="B100" s="49" t="s">
-        <v>106</v>
+        <v>99</v>
       </c>
       <c r="C100" s="46">
         <v>9789862164075</v>
       </c>
       <c r="D100" s="11" t="s">
-        <v>105</v>
+        <v>98</v>
       </c>
       <c r="E100" s="6" t="s">
-        <v>82</v>
+        <v>76</v>
       </c>
       <c r="F100" s="4" t="s">
-        <v>168</v>
+        <v>159</v>
       </c>
       <c r="G100" s="6"/>
       <c r="H100" s="6"/>
@@ -5279,24 +5266,24 @@
       <c r="U100" s="6"/>
       <c r="V100" s="6"/>
     </row>
-    <row r="101" spans="1:22" s="5" customFormat="1" x14ac:dyDescent="0.4">
-      <c r="A101" s="39" t="s">
-        <v>90</v>
+    <row r="101" spans="1:22" x14ac:dyDescent="0.4">
+      <c r="A101" s="47" t="s">
+        <v>164</v>
       </c>
       <c r="B101" s="4" t="s">
-        <v>91</v>
+        <v>84</v>
       </c>
       <c r="C101" s="12">
         <v>9789864893751</v>
       </c>
       <c r="D101" s="4" t="s">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="E101" s="39" t="s">
-        <v>82</v>
+        <v>76</v>
       </c>
       <c r="F101" s="4" t="s">
-        <v>168</v>
+        <v>159</v>
       </c>
       <c r="G101" s="6"/>
       <c r="H101" s="6"/>
@@ -5315,24 +5302,24 @@
       <c r="U101" s="6"/>
       <c r="V101" s="6"/>
     </row>
-    <row r="102" spans="1:22" s="5" customFormat="1" x14ac:dyDescent="0.4">
-      <c r="A102" s="39" t="s">
-        <v>90</v>
+    <row r="102" spans="1:22" x14ac:dyDescent="0.4">
+      <c r="A102" s="47" t="s">
+        <v>164</v>
       </c>
       <c r="B102" s="6" t="s">
-        <v>92</v>
+        <v>85</v>
       </c>
       <c r="C102" s="23">
         <v>9789869533492</v>
       </c>
       <c r="D102" s="6" t="s">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="E102" s="6" t="s">
-        <v>82</v>
+        <v>76</v>
       </c>
       <c r="F102" s="4" t="s">
-        <v>168</v>
+        <v>159</v>
       </c>
       <c r="G102" s="6"/>
       <c r="H102" s="6"/>
@@ -5351,24 +5338,24 @@
       <c r="U102" s="6"/>
       <c r="V102" s="6"/>
     </row>
-    <row r="103" spans="1:22" s="5" customFormat="1" x14ac:dyDescent="0.4">
-      <c r="A103" s="39" t="s">
-        <v>90</v>
+    <row r="103" spans="1:22" x14ac:dyDescent="0.4">
+      <c r="A103" s="47" t="s">
+        <v>164</v>
       </c>
       <c r="B103" s="6" t="s">
-        <v>93</v>
+        <v>86</v>
       </c>
       <c r="C103" s="23">
         <v>9789865406028</v>
       </c>
       <c r="D103" s="17" t="s">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="E103" s="6" t="s">
-        <v>82</v>
+        <v>76</v>
       </c>
       <c r="F103" s="4" t="s">
-        <v>168</v>
+        <v>159</v>
       </c>
       <c r="G103" s="6"/>
       <c r="H103" s="6"/>
@@ -5387,24 +5374,24 @@
       <c r="U103" s="6"/>
       <c r="V103" s="6"/>
     </row>
-    <row r="104" spans="1:22" s="5" customFormat="1" ht="18" x14ac:dyDescent="0.4">
-      <c r="A104" s="39" t="s">
-        <v>90</v>
+    <row r="104" spans="1:22" ht="18" x14ac:dyDescent="0.4">
+      <c r="A104" s="47" t="s">
+        <v>164</v>
       </c>
       <c r="B104" s="49" t="s">
-        <v>94</v>
+        <v>87</v>
       </c>
       <c r="C104" s="46">
         <v>9789863596585</v>
       </c>
       <c r="D104" s="4" t="s">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="E104" s="6" t="s">
-        <v>82</v>
+        <v>76</v>
       </c>
       <c r="F104" s="4" t="s">
-        <v>168</v>
+        <v>159</v>
       </c>
       <c r="G104" s="6"/>
       <c r="H104" s="6"/>
@@ -5423,24 +5410,24 @@
       <c r="U104" s="6"/>
       <c r="V104" s="6"/>
     </row>
-    <row r="105" spans="1:22" s="5" customFormat="1" x14ac:dyDescent="0.4">
-      <c r="A105" s="39" t="s">
-        <v>90</v>
+    <row r="105" spans="1:22" x14ac:dyDescent="0.4">
+      <c r="A105" s="47" t="s">
+        <v>164</v>
       </c>
       <c r="B105" s="6" t="s">
-        <v>95</v>
+        <v>88</v>
       </c>
       <c r="C105" s="23">
         <v>9789573261537</v>
       </c>
       <c r="D105" s="4" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="E105" s="39" t="s">
-        <v>82</v>
+        <v>76</v>
       </c>
       <c r="F105" s="4" t="s">
-        <v>168</v>
+        <v>159</v>
       </c>
       <c r="G105" s="50"/>
       <c r="H105" s="50"/>
@@ -5459,24 +5446,24 @@
       <c r="U105" s="50"/>
       <c r="V105" s="50"/>
     </row>
-    <row r="106" spans="1:22" s="5" customFormat="1" x14ac:dyDescent="0.4">
-      <c r="A106" s="39" t="s">
-        <v>90</v>
+    <row r="106" spans="1:22" x14ac:dyDescent="0.4">
+      <c r="A106" s="47" t="s">
+        <v>164</v>
       </c>
       <c r="B106" s="4" t="s">
-        <v>96</v>
+        <v>89</v>
       </c>
       <c r="C106" s="12">
         <v>9789573263296</v>
       </c>
       <c r="D106" s="6" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="E106" s="39" t="s">
-        <v>82</v>
+        <v>76</v>
       </c>
       <c r="F106" s="4" t="s">
-        <v>168</v>
+        <v>159</v>
       </c>
       <c r="G106" s="6"/>
       <c r="H106" s="6"/>
@@ -5495,24 +5482,24 @@
       <c r="U106" s="6"/>
       <c r="V106" s="6"/>
     </row>
-    <row r="107" spans="1:22" s="5" customFormat="1" x14ac:dyDescent="0.4">
-      <c r="A107" s="39" t="s">
+    <row r="107" spans="1:22" x14ac:dyDescent="0.4">
+      <c r="A107" s="47" t="s">
+        <v>164</v>
+      </c>
+      <c r="B107" s="4" t="s">
         <v>90</v>
       </c>
-      <c r="B107" s="4" t="s">
-        <v>97</v>
-      </c>
       <c r="C107" s="12" t="s">
-        <v>98</v>
+        <v>91</v>
       </c>
       <c r="D107" s="4" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="E107" s="39" t="s">
-        <v>82</v>
+        <v>76</v>
       </c>
       <c r="F107" s="4" t="s">
-        <v>168</v>
+        <v>159</v>
       </c>
       <c r="G107" s="6"/>
       <c r="H107" s="6"/>
@@ -5531,24 +5518,24 @@
       <c r="U107" s="6"/>
       <c r="V107" s="6"/>
     </row>
-    <row r="108" spans="1:22" s="5" customFormat="1" x14ac:dyDescent="0.4">
-      <c r="A108" s="39" t="s">
-        <v>90</v>
+    <row r="108" spans="1:22" x14ac:dyDescent="0.4">
+      <c r="A108" s="47" t="s">
+        <v>164</v>
       </c>
       <c r="B108" s="6" t="s">
-        <v>99</v>
+        <v>92</v>
       </c>
       <c r="C108" s="16">
         <v>9786269673360</v>
       </c>
       <c r="D108" s="6" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="E108" s="39" t="s">
-        <v>82</v>
+        <v>76</v>
       </c>
       <c r="F108" s="4" t="s">
-        <v>168</v>
+        <v>159</v>
       </c>
       <c r="G108" s="6"/>
       <c r="H108" s="6"/>
@@ -5568,43 +5555,43 @@
       <c r="V108" s="6"/>
     </row>
     <row r="109" spans="1:22" s="4" customFormat="1" x14ac:dyDescent="0.4">
-      <c r="A109" s="39" t="s">
-        <v>90</v>
+      <c r="A109" s="47" t="s">
+        <v>164</v>
       </c>
       <c r="B109" s="6" t="s">
-        <v>100</v>
+        <v>93</v>
       </c>
       <c r="C109" s="23">
         <v>9789861755267</v>
       </c>
       <c r="D109" s="6" t="s">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="E109" s="6" t="s">
-        <v>71</v>
+        <v>65</v>
       </c>
       <c r="F109" s="4" t="s">
-        <v>168</v>
-      </c>
-    </row>
-    <row r="110" spans="1:22" s="5" customFormat="1" ht="18" x14ac:dyDescent="0.4">
-      <c r="A110" s="39" t="s">
-        <v>90</v>
+        <v>159</v>
+      </c>
+    </row>
+    <row r="110" spans="1:22" ht="18" x14ac:dyDescent="0.4">
+      <c r="A110" s="47" t="s">
+        <v>164</v>
       </c>
       <c r="B110" s="51" t="s">
-        <v>101</v>
+        <v>94</v>
       </c>
       <c r="C110" s="46">
         <v>9789861372242</v>
       </c>
       <c r="D110" s="11" t="s">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="E110" s="6" t="s">
-        <v>51</v>
+        <v>47</v>
       </c>
       <c r="F110" s="4" t="s">
-        <v>168</v>
+        <v>159</v>
       </c>
       <c r="G110" s="6"/>
       <c r="H110" s="6"/>
@@ -5623,24 +5610,24 @@
       <c r="U110" s="6"/>
       <c r="V110" s="6"/>
     </row>
-    <row r="111" spans="1:22" s="5" customFormat="1" x14ac:dyDescent="0.4">
-      <c r="A111" s="39" t="s">
-        <v>90</v>
+    <row r="111" spans="1:22" x14ac:dyDescent="0.4">
+      <c r="A111" s="47" t="s">
+        <v>164</v>
       </c>
       <c r="B111" s="22" t="s">
-        <v>102</v>
+        <v>95</v>
       </c>
       <c r="C111" s="23">
         <v>9789573289982</v>
       </c>
       <c r="D111" s="11" t="s">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="E111" s="4" t="s">
-        <v>82</v>
+        <v>76</v>
       </c>
       <c r="F111" s="4" t="s">
-        <v>168</v>
+        <v>159</v>
       </c>
       <c r="G111" s="6"/>
       <c r="H111" s="6"/>
@@ -5659,24 +5646,24 @@
       <c r="U111" s="6"/>
       <c r="V111" s="6"/>
     </row>
-    <row r="112" spans="1:22" s="5" customFormat="1" ht="34" x14ac:dyDescent="0.4">
-      <c r="A112" s="39" t="s">
-        <v>90</v>
+    <row r="112" spans="1:22" ht="34" x14ac:dyDescent="0.4">
+      <c r="A112" s="47" t="s">
+        <v>164</v>
       </c>
       <c r="B112" s="11" t="s">
-        <v>103</v>
+        <v>96</v>
       </c>
       <c r="C112" s="10">
         <v>9789864778539</v>
       </c>
       <c r="D112" s="4" t="s">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="E112" s="39" t="s">
-        <v>82</v>
+        <v>76</v>
       </c>
       <c r="F112" s="4" t="s">
-        <v>168</v>
+        <v>159</v>
       </c>
       <c r="G112" s="6"/>
       <c r="H112" s="6"/>
@@ -5695,24 +5682,24 @@
       <c r="U112" s="6"/>
       <c r="V112" s="6"/>
     </row>
-    <row r="113" spans="1:22" s="5" customFormat="1" ht="34" x14ac:dyDescent="0.4">
-      <c r="A113" s="39" t="s">
-        <v>90</v>
+    <row r="113" spans="1:22" ht="34" x14ac:dyDescent="0.4">
+      <c r="A113" s="47" t="s">
+        <v>164</v>
       </c>
       <c r="B113" s="22" t="s">
-        <v>107</v>
+        <v>100</v>
       </c>
       <c r="C113" s="23">
         <v>9786263182219</v>
       </c>
       <c r="D113" s="11" t="s">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="E113" s="39" t="s">
-        <v>82</v>
+        <v>76</v>
       </c>
       <c r="F113" s="4" t="s">
-        <v>168</v>
+        <v>159</v>
       </c>
       <c r="G113" s="6"/>
       <c r="H113" s="6"/>
@@ -5733,213 +5720,213 @@
     </row>
   </sheetData>
   <phoneticPr fontId="1" type="noConversion"/>
+  <conditionalFormatting sqref="B88">
+    <cfRule type="duplicateValues" dxfId="93" priority="8"/>
+  </conditionalFormatting>
   <conditionalFormatting sqref="B4">
-    <cfRule type="duplicateValues" dxfId="93" priority="73"/>
     <cfRule type="duplicateValues" dxfId="92" priority="74"/>
+    <cfRule type="duplicateValues" dxfId="91" priority="73"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B17">
-    <cfRule type="duplicateValues" dxfId="91" priority="65"/>
-    <cfRule type="duplicateValues" dxfId="90" priority="66"/>
+    <cfRule type="duplicateValues" dxfId="90" priority="65"/>
     <cfRule type="duplicateValues" dxfId="89" priority="67"/>
+    <cfRule type="duplicateValues" dxfId="88" priority="66"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B36">
+    <cfRule type="duplicateValues" dxfId="87" priority="40"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B37">
+    <cfRule type="duplicateValues" dxfId="86" priority="39"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B38">
+    <cfRule type="duplicateValues" dxfId="85" priority="36"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B41">
+    <cfRule type="duplicateValues" dxfId="84" priority="43"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B43 B45:B46 B34:B35 B39:B40">
+    <cfRule type="duplicateValues" dxfId="83" priority="50"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B55 B53">
+    <cfRule type="duplicateValues" dxfId="82" priority="51"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B59">
+    <cfRule type="duplicateValues" dxfId="81" priority="21"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B60">
+    <cfRule type="duplicateValues" dxfId="80" priority="20"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B61">
+    <cfRule type="duplicateValues" dxfId="79" priority="22"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B66">
+    <cfRule type="duplicateValues" dxfId="78" priority="9"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B85">
+    <cfRule type="duplicateValues" dxfId="77" priority="5"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B62:C62 B71:C81 B58 B67:C67">
+    <cfRule type="duplicateValues" dxfId="76" priority="33"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B68:C69">
+    <cfRule type="duplicateValues" dxfId="75" priority="29"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B86:C87 B82:C84 B89:C97">
+    <cfRule type="duplicateValues" dxfId="74" priority="7"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="C1">
+    <cfRule type="duplicateValues" dxfId="73" priority="60"/>
+    <cfRule type="duplicateValues" dxfId="72" priority="61"/>
+    <cfRule type="duplicateValues" dxfId="71" priority="59"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="C2 C9:C16 C18:C19 C6 C26:C31 C21">
-    <cfRule type="duplicateValues" dxfId="88" priority="95"/>
+    <cfRule type="duplicateValues" dxfId="70" priority="95"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="C5">
-    <cfRule type="duplicateValues" dxfId="87" priority="70"/>
-    <cfRule type="duplicateValues" dxfId="86" priority="71"/>
-    <cfRule type="duplicateValues" dxfId="85" priority="72"/>
+    <cfRule type="duplicateValues" dxfId="69" priority="70"/>
+    <cfRule type="duplicateValues" dxfId="68" priority="72"/>
+    <cfRule type="duplicateValues" dxfId="67" priority="71"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="C7">
-    <cfRule type="duplicateValues" dxfId="84" priority="68"/>
-    <cfRule type="duplicateValues" dxfId="83" priority="69"/>
+    <cfRule type="duplicateValues" dxfId="66" priority="68"/>
+    <cfRule type="duplicateValues" dxfId="65" priority="69"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="C8">
-    <cfRule type="duplicateValues" dxfId="82" priority="75"/>
-    <cfRule type="duplicateValues" dxfId="81" priority="76"/>
+    <cfRule type="duplicateValues" dxfId="64" priority="75"/>
+    <cfRule type="duplicateValues" dxfId="63" priority="76"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="C9 C2 C11:C15 C18:C19 C6 C26:C31 C21">
-    <cfRule type="duplicateValues" dxfId="80" priority="93"/>
-    <cfRule type="duplicateValues" dxfId="79" priority="94"/>
+    <cfRule type="duplicateValues" dxfId="62" priority="93"/>
+    <cfRule type="duplicateValues" dxfId="61" priority="94"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="C10">
-    <cfRule type="duplicateValues" dxfId="78" priority="87"/>
-    <cfRule type="duplicateValues" dxfId="77" priority="88"/>
+    <cfRule type="duplicateValues" dxfId="60" priority="88"/>
+    <cfRule type="duplicateValues" dxfId="59" priority="87"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="C16">
-    <cfRule type="duplicateValues" dxfId="76" priority="89"/>
-    <cfRule type="duplicateValues" dxfId="75" priority="90"/>
+    <cfRule type="duplicateValues" dxfId="58" priority="89"/>
+    <cfRule type="duplicateValues" dxfId="57" priority="90"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="C17">
-    <cfRule type="duplicateValues" dxfId="74" priority="62"/>
-    <cfRule type="duplicateValues" dxfId="73" priority="63"/>
-    <cfRule type="duplicateValues" dxfId="72" priority="64"/>
+    <cfRule type="duplicateValues" dxfId="56" priority="63"/>
+    <cfRule type="duplicateValues" dxfId="55" priority="62"/>
+    <cfRule type="duplicateValues" dxfId="54" priority="64"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="C20">
-    <cfRule type="duplicateValues" dxfId="71" priority="83"/>
-    <cfRule type="duplicateValues" dxfId="70" priority="84"/>
+    <cfRule type="duplicateValues" dxfId="53" priority="83"/>
+    <cfRule type="duplicateValues" dxfId="52" priority="84"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="C22">
-    <cfRule type="duplicateValues" dxfId="69" priority="85"/>
-    <cfRule type="duplicateValues" dxfId="68" priority="86"/>
+    <cfRule type="duplicateValues" dxfId="51" priority="85"/>
+    <cfRule type="duplicateValues" dxfId="50" priority="86"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="C23">
-    <cfRule type="duplicateValues" dxfId="67" priority="81"/>
-    <cfRule type="duplicateValues" dxfId="66" priority="82"/>
+    <cfRule type="duplicateValues" dxfId="49" priority="81"/>
+    <cfRule type="duplicateValues" dxfId="48" priority="82"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="C24:C25">
-    <cfRule type="duplicateValues" dxfId="65" priority="91"/>
-    <cfRule type="duplicateValues" dxfId="64" priority="92"/>
+    <cfRule type="duplicateValues" dxfId="47" priority="91"/>
+    <cfRule type="duplicateValues" dxfId="46" priority="92"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="C32">
-    <cfRule type="duplicateValues" dxfId="63" priority="79"/>
-    <cfRule type="duplicateValues" dxfId="62" priority="80"/>
+    <cfRule type="duplicateValues" dxfId="45" priority="79"/>
+    <cfRule type="duplicateValues" dxfId="44" priority="80"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="C33">
-    <cfRule type="duplicateValues" dxfId="61" priority="77"/>
-    <cfRule type="duplicateValues" dxfId="60" priority="78"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="C1">
-    <cfRule type="duplicateValues" dxfId="59" priority="59"/>
-    <cfRule type="duplicateValues" dxfId="58" priority="60"/>
-    <cfRule type="duplicateValues" dxfId="57" priority="61"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="B36">
-    <cfRule type="duplicateValues" dxfId="56" priority="40"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="B37">
-    <cfRule type="duplicateValues" dxfId="55" priority="39"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="B38">
-    <cfRule type="duplicateValues" dxfId="54" priority="36"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="B41">
-    <cfRule type="duplicateValues" dxfId="53" priority="43"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="B43 B45:B46 B34:B35 B39:B40">
-    <cfRule type="duplicateValues" dxfId="52" priority="50"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="B55 B53">
-    <cfRule type="duplicateValues" dxfId="51" priority="51"/>
+    <cfRule type="duplicateValues" dxfId="43" priority="78"/>
+    <cfRule type="duplicateValues" dxfId="42" priority="77"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="C38">
-    <cfRule type="duplicateValues" dxfId="50" priority="37"/>
-    <cfRule type="duplicateValues" dxfId="49" priority="38"/>
+    <cfRule type="duplicateValues" dxfId="41" priority="37"/>
+    <cfRule type="duplicateValues" dxfId="40" priority="38"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="C38:C57 C34">
-    <cfRule type="duplicateValues" dxfId="48" priority="56"/>
+    <cfRule type="duplicateValues" dxfId="39" priority="56"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="C41">
-    <cfRule type="duplicateValues" dxfId="47" priority="44"/>
-    <cfRule type="duplicateValues" dxfId="46" priority="45"/>
+    <cfRule type="duplicateValues" dxfId="38" priority="45"/>
+    <cfRule type="duplicateValues" dxfId="37" priority="44"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="C43 C45:C46 C34 C39:C40 C50">
-    <cfRule type="duplicateValues" dxfId="45" priority="57"/>
-    <cfRule type="duplicateValues" dxfId="44" priority="58"/>
+    <cfRule type="duplicateValues" dxfId="36" priority="57"/>
+    <cfRule type="duplicateValues" dxfId="35" priority="58"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="C44 C42">
-    <cfRule type="duplicateValues" dxfId="43" priority="46"/>
-    <cfRule type="duplicateValues" dxfId="42" priority="47"/>
+    <cfRule type="duplicateValues" dxfId="34" priority="46"/>
+    <cfRule type="duplicateValues" dxfId="33" priority="47"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="C51 C49">
-    <cfRule type="duplicateValues" dxfId="41" priority="41"/>
-    <cfRule type="duplicateValues" dxfId="40" priority="42"/>
+    <cfRule type="duplicateValues" dxfId="32" priority="42"/>
+    <cfRule type="duplicateValues" dxfId="31" priority="41"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="C52 C56:C57">
-    <cfRule type="duplicateValues" dxfId="39" priority="54"/>
-    <cfRule type="duplicateValues" dxfId="38" priority="55"/>
+    <cfRule type="duplicateValues" dxfId="30" priority="54"/>
+    <cfRule type="duplicateValues" dxfId="29" priority="55"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="C54 C47:C48">
-    <cfRule type="duplicateValues" dxfId="37" priority="48"/>
-    <cfRule type="duplicateValues" dxfId="36" priority="49"/>
+    <cfRule type="duplicateValues" dxfId="28" priority="49"/>
+    <cfRule type="duplicateValues" dxfId="27" priority="48"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="C55 C53">
-    <cfRule type="duplicateValues" dxfId="35" priority="52"/>
-    <cfRule type="duplicateValues" dxfId="34" priority="53"/>
+    <cfRule type="duplicateValues" dxfId="26" priority="52"/>
+    <cfRule type="duplicateValues" dxfId="25" priority="53"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B59">
-    <cfRule type="duplicateValues" dxfId="33" priority="21"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="B60">
-    <cfRule type="duplicateValues" dxfId="32" priority="20"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="B61">
-    <cfRule type="duplicateValues" dxfId="31" priority="22"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="B66">
-    <cfRule type="duplicateValues" dxfId="30" priority="9"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="B62:C62 B71:C81 B58 B67:C67">
-    <cfRule type="duplicateValues" dxfId="29" priority="33"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="B68:C69">
-    <cfRule type="duplicateValues" dxfId="28" priority="29"/>
+  <conditionalFormatting sqref="C62 C71 C66 C73 C77:C78">
+    <cfRule type="duplicateValues" dxfId="24" priority="35"/>
+    <cfRule type="duplicateValues" dxfId="23" priority="34"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="C63">
-    <cfRule type="duplicateValues" dxfId="27" priority="11"/>
-    <cfRule type="duplicateValues" dxfId="26" priority="12"/>
-    <cfRule type="duplicateValues" dxfId="25" priority="13"/>
+    <cfRule type="duplicateValues" dxfId="22" priority="13"/>
+    <cfRule type="duplicateValues" dxfId="21" priority="11"/>
+    <cfRule type="duplicateValues" dxfId="20" priority="12"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="C66">
-    <cfRule type="duplicateValues" dxfId="24" priority="10"/>
+    <cfRule type="duplicateValues" dxfId="19" priority="10"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="C67">
-    <cfRule type="duplicateValues" dxfId="23" priority="25"/>
-    <cfRule type="duplicateValues" dxfId="22" priority="26"/>
+    <cfRule type="duplicateValues" dxfId="18" priority="26"/>
+    <cfRule type="duplicateValues" dxfId="17" priority="25"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="C68:C69">
-    <cfRule type="duplicateValues" dxfId="21" priority="32"/>
+    <cfRule type="duplicateValues" dxfId="16" priority="32"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="C70">
-    <cfRule type="duplicateValues" dxfId="20" priority="14"/>
-    <cfRule type="duplicateValues" dxfId="19" priority="15"/>
-    <cfRule type="duplicateValues" dxfId="18" priority="16"/>
+    <cfRule type="duplicateValues" dxfId="15" priority="16"/>
+    <cfRule type="duplicateValues" dxfId="14" priority="15"/>
+    <cfRule type="duplicateValues" dxfId="13" priority="14"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="C74:C75 C72">
-    <cfRule type="duplicateValues" dxfId="17" priority="23"/>
-    <cfRule type="duplicateValues" dxfId="16" priority="24"/>
+    <cfRule type="duplicateValues" dxfId="12" priority="24"/>
+    <cfRule type="duplicateValues" dxfId="11" priority="23"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="C76">
-    <cfRule type="duplicateValues" dxfId="15" priority="27"/>
-    <cfRule type="duplicateValues" dxfId="14" priority="28"/>
+    <cfRule type="duplicateValues" dxfId="10" priority="28"/>
+    <cfRule type="duplicateValues" dxfId="9" priority="27"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="C79:C81">
-    <cfRule type="duplicateValues" dxfId="13" priority="30"/>
-    <cfRule type="duplicateValues" dxfId="12" priority="31"/>
+    <cfRule type="duplicateValues" dxfId="8" priority="31"/>
+    <cfRule type="duplicateValues" dxfId="7" priority="30"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="C82:C84 C86:C97">
+    <cfRule type="duplicateValues" dxfId="6" priority="6"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="C88">
+    <cfRule type="duplicateValues" dxfId="5" priority="4"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="C98 C100:C108 C110:C113">
+    <cfRule type="duplicateValues" dxfId="4" priority="3"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="C99">
+    <cfRule type="duplicateValues" dxfId="3" priority="1"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="C109">
+    <cfRule type="duplicateValues" dxfId="2" priority="2"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="G73">
-    <cfRule type="duplicateValues" dxfId="11" priority="19"/>
+    <cfRule type="duplicateValues" dxfId="1" priority="19"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="H70">
-    <cfRule type="duplicateValues" dxfId="10" priority="18"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="C62 C71 C66 C73 C77:C78">
-    <cfRule type="duplicateValues" dxfId="9" priority="34"/>
-    <cfRule type="duplicateValues" dxfId="8" priority="35"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="B85">
-    <cfRule type="duplicateValues" dxfId="7" priority="5"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="B86:C87 B82:C84 B89:C97">
-    <cfRule type="duplicateValues" dxfId="6" priority="7"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="C82:C84 C86:C97">
-    <cfRule type="duplicateValues" dxfId="5" priority="6"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="C88">
-    <cfRule type="duplicateValues" dxfId="4" priority="4"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="A88:B88">
-    <cfRule type="duplicateValues" dxfId="3" priority="8"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="C98 C100:C108 C110:C113">
-    <cfRule type="duplicateValues" dxfId="2" priority="3"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="C99">
-    <cfRule type="duplicateValues" dxfId="1" priority="1"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="C109">
-    <cfRule type="duplicateValues" dxfId="0" priority="2"/>
+    <cfRule type="duplicateValues" dxfId="0" priority="18"/>
   </conditionalFormatting>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
